--- a/docs/assets/cases/rules.xlsx
+++ b/docs/assets/cases/rules.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="206">
   <si>
     <t>status</t>
   </si>
@@ -167,7 +167,7 @@
     <t>[]</t>
   </si>
   <si>
-    <t>0.03267479999340139</t>
+    <t>0.05286455899477005</t>
   </si>
   <si>
     <t>{"profile": "production", "direction": "high_risk", "candidate_filter": {"conditions": [{"metric": "lift", "operator": "&gt;=", "value": 1.2}, {"metric": "event_count", "operator": "&gt;=", "value": 3.0}, {"metric": "coverage", "operator": "&gt;=", "value": 0.01}, {"metric": "coverage", "operator": "&lt;=", "value": 0.5}], "targets": "primary", "target_scope": "all", "slice_pass_rate": null}, "validation_filter": {"conditions": [{"metric": "lift", "operator": "&gt;=", "value": 2.0}, {"metric": "event_count", "operator": "&gt;=", "value": 3.0}, {"metric": "coverage", "operator": "&gt;=", "value": 0.01}, {"metric": "coverage", "operator": "&lt;=", "value": 0.5}], "targets": "primary", "target_scope": "all", "slice_pass_rate": 0.8}, "grade_filters": {}, "selection_strategy": "ranked", "top_k": 10, "max_candidates": 100000, "iou_threshold": 0.3, "batch_size": 100, "iou_batch_size": 512, "max_rounds": 10, "random_state": 42, "on_generator_error": "raise", "confidence_level": 0.95, "max_fdr": 0.05, "min_time_slices": 3}</t>
@@ -206,16 +206,16 @@
     <t>selection_round</t>
   </si>
   <si>
-    <t>mr_cb714e09ca8c064f8185</t>
-  </si>
-  <si>
-    <t>mr_20fa26e2262d26742d78</t>
-  </si>
-  <si>
-    <t>(((((("aux_score" != -999 AND "aux_score" &gt; 567.1738809810513) AND "main_score" != -999) AND "main_score" &lt;= 601.2262132556998) AND "main_score" &gt; 546.042988729658) AND "aux_score" IS NOT MISSING) AND "main_score" IS NOT MISSING)</t>
-  </si>
-  <si>
-    <t>(((((("aux_score" != -999 AND "aux_score" &gt; 567.1738809810513) AND "main_score" != -999) AND "main_score" &lt;= 653.7750315986514) AND "main_score" &gt; 601.2262132556998) AND "aux_score" IS NOT MISSING) AND "main_score" IS NOT MISSING)</t>
+    <t>mr_7bdb03abe2bdaf07f897</t>
+  </si>
+  <si>
+    <t>mr_17ee9fe9490cfed4c8c6</t>
+  </si>
+  <si>
+    <t>(((((("aux_score" != -999 AND "aux_score" &lt;= 1.7976931348623157e+308) AND "aux_score" &gt; 567.1738809810513) AND "main_score" &lt;= 601.2262132556998) AND "main_score" &gt; 546.042988729658) AND "aux_score" IS NOT MISSING) AND "main_score" IS NOT MISSING)</t>
+  </si>
+  <si>
+    <t>(((((("aux_score" != -999 AND "aux_score" &lt;= 1.7976931348623157e+308) AND "aux_score" &gt; 567.1738809810513) AND "main_score" &lt;= 653.7750315986514) AND "main_score" &gt; 601.2262132556998) AND "aux_score" IS NOT MISSING) AND "main_score" IS NOT MISSING)</t>
   </si>
   <si>
     <t>cross_discovery</t>
@@ -281,19 +281,19 @@
     <t>time_slice_pass_rate</t>
   </si>
   <si>
-    <t>mr_8664f1fa21c9c7ac8a92</t>
-  </si>
-  <si>
-    <t>mr_adcb27865a5ad7dbe5ef</t>
+    <t>mr_ad799e0c85ff11828d91</t>
+  </si>
+  <si>
+    <t>mr_c67ebed12b349c6732e7</t>
   </si>
   <si>
     <t>mr_60edcd64fb81d6441861</t>
   </si>
   <si>
-    <t>(((((("aux_score" != -999 AND "aux_score" &lt;= 432.41255966198844) AND "main_score" != -999) AND "main_score" &lt;= 601.2262132556998) AND "main_score" &gt; 546.042988729658) AND "aux_score" IS NOT MISSING) AND "main_score" IS NOT MISSING)</t>
-  </si>
-  <si>
-    <t>((((("aux_score" != -999 AND "aux_score" &gt; 567.1738809810513) AND "main_score" != -999) AND "main_score" &gt; 653.7750315986514) AND "aux_score" IS NOT MISSING) AND "main_score" IS NOT MISSING)</t>
+    <t>(((((("aux_score" != -999 AND "aux_score" &lt;= 432.41255966198844) AND "aux_score" &gt;= -1.7976931348623157e+308) AND "main_score" &lt;= 601.2262132556998) AND "main_score" &gt; 546.042988729658) AND "aux_score" IS NOT MISSING) AND "main_score" IS NOT MISSING)</t>
+  </si>
+  <si>
+    <t>(((((("aux_score" != -999 AND "aux_score" &lt;= 1.7976931348623157e+308) AND "aux_score" &gt; 567.1738809810513) AND "main_score" &lt;= 1.7976931348623157e+308) AND "main_score" &gt; 653.7750315986514) AND "aux_score" IS NOT MISSING) AND "main_score" IS NOT MISSING)</t>
   </si>
   <si>
     <t>("aux_score" &gt; 900 AND "main_score" &gt; 900)</t>
@@ -425,10 +425,10 @@
     <t>explanation</t>
   </si>
   <si>
-    <t>第 1 条规则命中 322 个样本，覆盖率 5.80%，事件数 167，事件率 51.86%，Lift 3.264，95% 保守区间 [2.976, 3.550]，q 值 0.0000。</t>
-  </si>
-  <si>
-    <t>第 2 条规则命中 345 个样本，覆盖率 6.22%，事件数 139，事件率 40.29%，Lift 2.536，95% 保守区间 [2.268, 2.813]，q 值 0.0000。</t>
+    <t>第 1 条规则命中 316 个样本，覆盖率 5.69%，事件数 167，事件率 52.85%，Lift 3.326，95% 保守区间 [3.035, 3.614]，q 值 0.0000。</t>
+  </si>
+  <si>
+    <t>第 2 条规则命中 339 个样本，覆盖率 6.11%，事件数 137，事件率 40.41%，Lift 2.543，95% 保守区间 [2.273, 2.823]，q 值 0.0000。</t>
   </si>
   <si>
     <t>feature</t>
@@ -506,6 +506,15 @@
     <t>independence</t>
   </si>
   <si>
+    <t>seed</t>
+  </si>
+  <si>
+    <t>weight_definition</t>
+  </si>
+  <si>
+    <t>binning_origin</t>
+  </si>
+  <si>
     <t>candidate_origins</t>
   </si>
   <si>
@@ -518,7 +527,7 @@
     <t>"synthetic-consumer-credit-20261001"</t>
   </si>
   <si>
-    <t>"模拟申请，每行独立 sample_id"</t>
+    <t>"one synthetic application; unique sample_id"</t>
   </si>
   <si>
     <t>"unknown"</t>
@@ -536,19 +545,31 @@
     <t>{"bad30":{"definition":"模拟30日违约","performance_window":"30天"},"late60":{"definition":"模拟60日逾期","performance_window":"60天"}}</t>
   </si>
   <si>
-    <t>{"discovery":"2026-01至03，6000独立行；确定分段及候选","validation":"2026-04至06，6000独立行；一次独立门禁检验","observation":"2026-07至09，6000独立行；仅交叉观察，不参与选择"}</t>
+    <t>{"discovery":"1–3月；参考分箱与候选发现","validation":"4–6月；独立验证，不重新拟合分箱或选择候选","observation":"7–9月；bad30 有模拟标签，late60 全未表现"}</t>
   </si>
   <si>
     <t>{"main_score":"lower_risk","aux_score":"higher_risk"}</t>
   </si>
   <si>
-    <t>"模拟申请金额，不代表损失或利润"</t>
+    <t>"模拟申请金额 CNY；不是损失、利润或预期收益"</t>
   </si>
   <si>
     <t>"不同 sample_id 和时间，不从验证或观察重新挑选候选；并非真实业务效果"</t>
   </si>
   <si>
-    <t>{"mr_cb714e09ca8c064f8185":{"kind":"development_cell","reference":{"report_id":"066dccc0-b803-4f2a-8f3c-2ace86cf0ada","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"discovery","period":"202601","target":"bad30","x_bin":"b1","y_bin":"b3"}}}},"mr_20fa26e2262d26742d78":{"kind":"development_cell","reference":{"report_id":"066dccc0-b803-4f2a-8f3c-2ace86cf0ada","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"discovery","period":"202601","target":"bad30","x_bin":"b2","y_bin":"b3"}}}},"mr_8664f1fa21c9c7ac8a92":{"kind":"development_cell","reference":{"report_id":"066dccc0-b803-4f2a-8f3c-2ace86cf0ada","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"discovery","period":"202601","target":"bad30","x_bin":"b1","y_bin":"b0"}}}},"mr_adcb27865a5ad7dbe5ef":{"kind":"development_cell","reference":{"report_id":"066dccc0-b803-4f2a-8f3c-2ace86cf0ada","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"discovery","period":"202601","target":"bad30","x_bin":"b3","y_bin":"b3"}}}},"mr_60edcd64fb81d6441861":{"kind":"sample_insufficiency_check","cross_reference":null,"limitation":"手工覆盖压力候选，无交叉格子对应，不制造证据链"}}</t>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>20261001</t>
+  </si>
+  <si>
+    <t>"模拟分析权重；与原始申请人数分别保存"</t>
+  </si>
+  <si>
+    <t>"discovery only; frozen definitions"</t>
+  </si>
+  <si>
+    <t>{"mr_7bdb03abe2bdaf07f897":{"kind":"development_cell","region":{"x_bin":"b1","y_bin":"b3"},"member_check":{"verified":true,"scope":"all supplied rows; exact sample_id membership","member_count":1128,"members_by_dataset":[{"dataset":"discovery","sample_count":385,"observed_sample_count":348},{"dataset":"observation","sample_count":391,"observed_sample_count":365},{"dataset":"validation","sample_count":352,"observed_sample_count":316}]},"reference":{"report_id":"cba02fb3-e2e3-44ae-8c72-32ab920fd80c","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"discovery","period":"202601","target":"bad30","x_bin":"b1","y_bin":"b3"}}}},"mr_17ee9fe9490cfed4c8c6":{"kind":"development_cell","region":{"x_bin":"b2","y_bin":"b3"},"member_check":{"verified":true,"scope":"all supplied rows; exact sample_id membership","member_count":1114,"members_by_dataset":[{"dataset":"discovery","sample_count":382,"observed_sample_count":349},{"dataset":"observation","sample_count":365,"observed_sample_count":338},{"dataset":"validation","sample_count":367,"observed_sample_count":339}]},"reference":{"report_id":"cba02fb3-e2e3-44ae-8c72-32ab920fd80c","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"discovery","period":"202601","target":"bad30","x_bin":"b2","y_bin":"b3"}}}},"mr_ad799e0c85ff11828d91":{"kind":"development_cell","region":{"x_bin":"b1","y_bin":"b0"},"member_check":{"verified":true,"scope":"all supplied rows; exact sample_id membership","member_count":1123,"members_by_dataset":[{"dataset":"discovery","sample_count":385,"observed_sample_count":356},{"dataset":"observation","sample_count":345,"observed_sample_count":313},{"dataset":"validation","sample_count":393,"observed_sample_count":358}]},"reference":{"report_id":"cba02fb3-e2e3-44ae-8c72-32ab920fd80c","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"discovery","period":"202601","target":"bad30","x_bin":"b1","y_bin":"b0"}}}},"mr_c67ebed12b349c6732e7":{"kind":"development_cell","region":{"x_bin":"b3","y_bin":"b3"},"member_check":{"verified":true,"scope":"all supplied rows; exact sample_id membership","member_count":1105,"members_by_dataset":[{"dataset":"discovery","sample_count":337,"observed_sample_count":307},{"dataset":"observation","sample_count":374,"observed_sample_count":344},{"dataset":"validation","sample_count":394,"observed_sample_count":372}]},"reference":{"report_id":"cba02fb3-e2e3-44ae-8c72-32ab920fd80c","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"discovery","period":"202601","target":"bad30","x_bin":"b3","y_bin":"b3"}}}},"mr_60edcd64fb81d6441861":{"kind":"sample_insufficiency_check","cross_reference":null,"limitation":"手工覆盖压力候选，无交叉格子对应，不制造证据链"}}</t>
   </si>
   <si>
     <t>"只计算 validation 时间切片；没有客群或规则 observation 评估"</t>
@@ -590,7 +611,7 @@
     <t>default_ai_queries</t>
   </si>
   <si>
-    <t>"a7c565bd-eb83-408b-88e6-791eccd5c87f"</t>
+    <t>"12260b98-9fab-4dc4-86e7-bd13ef84fa1a"</t>
   </si>
   <si>
     <t>"rule"</t>
@@ -602,7 +623,7 @@
     <t>{"summary":{"rows":1,"grain":"one mining run (or benchmark summary); no feature-level metrics","schema_version":1,"fields":{"status":{"dtype":"String","unit":"state","meaning":"summary success/no_rules；候选 selected/rejected/candidate/deferred；结合 reason 和 rejection_stage","null":"unavailable; inspect status and report parameters"},"candidate_count":{"dtype":"Int64","unit":"count","meaning":"候选审计行数；cascade 包含同一 rule_id 在不同轮次的审计，不是去重规则数","null":"unavailable; inspect status and report parameters"},"selected_count":{"dtype":"Int64","unit":"count","meaning":"最终 RuleSet 中入选规则数；no_rules 为 0","null":"unavailable; inspect status and report parameters"},"validation_status":{"dtype":"String","unit":"state","meaning":"independent 或 in_sample；验证样本独立性由调用方保证","null":"unavailable; inspect status and report parameters"},"profile":{"dtype":"String","unit":"category","meaning":"实际 explore / production 门禁；报告不改阈值","null":"unavailable; inspect status and report parameters"},"qualification":{"dtype":"String","unit":"state","meaning":"计算时 RuleSet 资格；快照恢复不会重建部署资格","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_query":"unsupported"},"rules":{"rows":2,"grain":"final rule_id / selection rank; grades are rule membership, not metrics","schema_version":1,"fields":{"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"expression":{"dtype":"String","unit":"definition","meaning":"既有 DSL 规范表达式；不执行报告文本","null":"unavailable; inspect status and report parameters"},"rank":{"dtype":"Int64","unit":"ordinal","meaning":"最终规则集的 1 起始顺序；cumulative 使用此前全部规则的并集","null":"unavailable; inspect status and report parameters"},"source":{"dtype":"String","unit":"category","meaning":"规则生成来源；不是业务特征来源","null":"unavailable; inspect status and report parameters"},"labels":{"dtype":"List(String)","unit":"unknown","meaning":"已保存的 labels；未登记业务含义保持 unknown","null":"unavailable; inspect status and report parameters"},"grades":{"dtype":"List(String)","unit":"category","meaning":"既有 RuleSet 等级成员列表","null":"unavailable; inspect status and report parameters"},"generation_round":{"dtype":"Int64","unit":"ordinal","meaning":"候选生成轮次；相同规则在不同轮次的审计不可合并","null":"unavailable; inspect status and report parameters"},"selection_round":{"dtype":"Int64","unit":"ordinal","meaning":"实际 cascade 入选轮次；未入选为 null","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_relation":{"table":"rule_features","key":"rule_id","feature":"feature","roles":{"rule_id":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次"}},"feature_query":"relation"},"candidates":{"rows":5,"grain":"candidate rule_id / generation_round when present; generator audit","schema_version":1,"fields":{"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"expression":{"dtype":"String","unit":"definition","meaning":"既有 DSL 规范表达式；不执行报告文本","null":"unavailable; inspect status and report parameters"},"sources":{"dtype":"String","unit":"category","meaning":"候选生成器／seed 来源；不是 feature_metadata.data_source","null":"unavailable; inspect status and report parameters"},"distinct_source_count":{"dtype":"Int64","unit":"count","meaning":"实际 distinct_source_count 整数计数；粒度见本表 grain","null":"unavailable; inspect status and report parameters"},"exact_duplicate_count":{"dtype":"Int64","unit":"count","meaning":"实际 exact_duplicate_count 整数计数；粒度见本表 grain","null":"unavailable; inspect status and report parameters"},"within_candidate_budget":{"dtype":"Boolean","unit":"boolean","meaning":"实际 within_candidate_budget 门禁结果；null 表示未执行或不适用","null":"unavailable; inspect status and report parameters"},"candidate_filter_passed":{"dtype":"Boolean","unit":"boolean","meaning":"实际 candidate_filter_passed 门禁结果；null 表示未执行或不适用","null":"unavailable; inspect status and report parameters"},"validation_filter_passed":{"dtype":"Boolean","unit":"boolean","meaning":"实际 validation_filter_passed 门禁结果；null 表示未执行或不适用","null":"unavailable; inspect status and report parameters"},"iou_filter_passed":{"dtype":"Boolean","unit":"boolean","meaning":"实际 iou_filter_passed 门禁结果；null 表示未执行或不适用","null":"unavailable; inspect status and report parameters"},"selection_rank":{"dtype":"Int64","unit":"ordinal","meaning":"实际选择顺序；未入选为 null","null":"unavailable; inspect status and report parameters"},"status":{"dtype":"String","unit":"state","meaning":"summary success/no_rules；候选 selected/rejected/candidate/deferred；结合 reason 和 rejection_stage","null":"unavailable; inspect status and report parameters"},"rejection_stage":{"dtype":"String","unit":"state_reason","meaning":"实际淘汰门禁阶段","null":"unavailable; inspect status and report parameters"},"reason":{"dtype":"String","unit":"state_reason","meaning":"真实候选淘汰原因；错误不转换为 no_rules","null":"unavailable; inspect status and report parameters"},"source_position":{"dtype":"Int64","unit":"ordinal","meaning":"实际 source_position 候选顺序；null 表示不适用","null":"unavailable; inspect status and report parameters"},"budget_position":{"dtype":"Int64","unit":"ordinal","meaning":"实际 budget_position 候选顺序；null 表示不适用","null":"unavailable; inspect status and report parameters"},"budget_strategy":{"dtype":"String","unit":"category","meaning":"已保存的 budget_strategy；未登记业务含义保持 unknown","null":"unavailable; inspect status and report parameters"},"q_value":{"dtype":"Float64","unit":"probability","meaning":"同数据范围、target、slice、group 候选检验族 BH 校正 q 值","null":"unavailable; inspect status and report parameters"},"lift_ci_lower":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率下界 / 同范围总体事件率；保守 Lift 下界","null":"unavailable; inspect status and report parameters"},"lift_ci_upper":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率上界 / 同范围总体事件率；保守 Lift 上界","null":"unavailable; inspect status and report parameters"},"temporal_assessed":{"dtype":"Boolean","unit":"boolean","meaning":"实际 temporal_assessed 门禁结果；null 表示未执行或不适用","null":"unavailable; inspect status and report parameters"},"temporal_passed":{"dtype":"Boolean","unit":"boolean","meaning":"实际 temporal_passed 门禁结果；null 表示未执行或不适用","null":"unavailable; inspect status and report parameters"},"time_slice_count":{"dtype":"Int64","unit":"count","meaning":"实际 time_slice_count 整数计数；粒度见本表 grain","null":"unavailable; inspect status and report parameters"},"time_slice_pass_rate":{"dtype":"Float64","unit":"ratio","meaning":"通过时间切片数 / 已评估时间切片数","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_relation":{"table":"rule_features","key":"rule_id","feature":"feature","roles":{"rule_id":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次"}},"feature_query":"relation"},"evaluation":{"rows":48,"grain":"dataset / rule_id / target / slice / group (hit, miss, total)","schema_version":1,"fields":{"dataset":{"dtype":"String","unit":"dimension","meaning":"实际保存的 train/validation/in_sample 范围；不推断未保存的逐轮剩余样本统计","null":"unavailable; inspect status and report parameters"},"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"target":{"dtype":"String","unit":"identifier","meaning":"真实标签列 ID；各 target 独立排除未表现标签","null":"unavailable; inspect status and report parameters"},"slice":{"dtype":"String","unit":"dimension","meaning":"__overall__ 或 evaluator 实际构造的时间／客群切片值","null":"unavailable; inspect status and report parameters"},"group":{"dtype":"String","unit":"dimension","meaning":"hit / miss / total；此列不是原始客群，客群见 slice","null":"unavailable; inspect status and report parameters"},"sample_count":{"dtype":"Int64","unit":"count","meaning":"当前 target 已表现样本数；group/slice/dataset 定义统计范围","null":"unavailable; inspect status and report parameters"},"event_count":{"dtype":"Int64","unit":"count","meaning":"当前范围已表现 label=1 样本数","null":"unavailable; inspect status and report parameters"},"coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前范围 sample_count / 同 dataset、target、slice 的 base sample_count；只含已表现样本","null":"unavailable; inspect status and report parameters"},"event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_count / sample_count；零分母 null","null":"unavailable; inspect status and report parameters"},"lift":{"dtype":"Float64","unit":"dimensionless","meaning":"event_rate / 同 dataset、target、slice 的 base event_rate；零分母 null","null":"unavailable; inspect status and report parameters"},"amount_total":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现样本金金额和；amount_col 未提供则 null；币种见 business_context","null":"unavailable; inspect status and report parameters"},"event_amount":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现 label=1 金额和；amount_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"amount_coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前 amount_total / 同范围 base amount_total","null":"unavailable; inspect status and report parameters"},"amount_event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_amount / amount_total；零分母 null","null":"unavailable; inspect status and report parameters"},"amount_lift":{"dtype":"Float64","unit":"dimensionless","meaning":"amount_event_rate / 同范围 base amount_event_rate","null":"unavailable; inspect status and report parameters"},"customer_count":{"dtype":"Int64","unit":"count","meaning":"当前已表现范围去重客户数；customer_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"event_customer_count":{"dtype":"Int64","unit":"count","meaning":"当前已表现 label=1 范围去重客户数","null":"unavailable; inspect status and report parameters"},"customer_coverage":{"dtype":"Float64","unit":"ratio","meaning":"customer_count / 同范围 base customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"customer_event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_customer_count / customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"customer_lift":{"dtype":"Float64","unit":"dimensionless","meaning":"customer_event_rate / 同范围 base customer_event_rate","null":"unavailable; inspect status and report parameters"},"event_rate_ci_lower":{"dtype":"Float64","unit":"ratio","meaning":"Wilson 事件率区间下界；confidence_level 见实际参数","null":"unavailable; inspect status and report parameters"},"event_rate_ci_upper":{"dtype":"Float64","unit":"ratio","meaning":"Wilson 事件率区间上界；confidence_level 见实际参数","null":"unavailable; inspect status and report parameters"},"lift_ci_lower":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率下界 / 同范围总体事件率；保守 Lift 下界","null":"unavailable; inspect status and report parameters"},"lift_ci_upper":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率上界 / 同范围总体事件率；保守 Lift 上界","null":"unavailable; inspect status and report parameters"},"p_value":{"dtype":"Float64","unit":"probability","meaning":"按 direction 的单侧事件富集检验 p 值；方法见 evaluator","null":"unavailable; inspect status and report parameters"},"q_value":{"dtype":"Float64","unit":"probability","meaning":"同数据范围、target、slice、group 候选检验族 BH 校正 q 值","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_relation":{"table":"rule_features","key":"rule_id","feature":"feature","roles":{"rule_id":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次"}},"feature_query":"relation"},"slices":{"rows":54,"grain":"dataset / rule_id / target / slice / group; slice encodes supplied time or segment","schema_version":1,"fields":{"dataset":{"dtype":"String","unit":"dimension","meaning":"实际保存的 train/validation/in_sample 范围；不推断未保存的逐轮剩余样本统计","null":"unavailable; inspect status and report parameters"},"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"target":{"dtype":"String","unit":"identifier","meaning":"真实标签列 ID；各 target 独立排除未表现标签","null":"unavailable; inspect status and report parameters"},"slice":{"dtype":"String","unit":"dimension","meaning":"__overall__ 或 evaluator 实际构造的时间／客群切片值","null":"unavailable; inspect status and report parameters"},"group":{"dtype":"String","unit":"dimension","meaning":"hit / miss / total；此列不是原始客群，客群见 slice","null":"unavailable; inspect status and report parameters"},"sample_count":{"dtype":"Int64","unit":"count","meaning":"当前 target 已表现样本数；group/slice/dataset 定义统计范围","null":"unavailable; inspect status and report parameters"},"event_count":{"dtype":"Int64","unit":"count","meaning":"当前范围已表现 label=1 样本数","null":"unavailable; inspect status and report parameters"},"coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前范围 sample_count / 同 dataset、target、slice 的 base sample_count；只含已表现样本","null":"unavailable; inspect status and report parameters"},"event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_count / sample_count；零分母 null","null":"unavailable; inspect status and report parameters"},"lift":{"dtype":"Float64","unit":"dimensionless","meaning":"event_rate / 同 dataset、target、slice 的 base event_rate；零分母 null","null":"unavailable; inspect status and report parameters"},"amount_total":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现样本金金额和；amount_col 未提供则 null；币种见 business_context","null":"unavailable; inspect status and report parameters"},"event_amount":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现 label=1 金额和；amount_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"amount_coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前 amount_total / 同范围 base amount_total","null":"unavailable; inspect status and report parameters"},"amount_event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_amount / amount_total；零分母 null","null":"unavailable; inspect status and report parameters"},"amount_lift":{"dtype":"Float64","unit":"dimensionless","meaning":"amount_event_rate / 同范围 base amount_event_rate","null":"unavailable; inspect status and report parameters"},"customer_count":{"dtype":"Int64","unit":"count","meaning":"当前已表现范围去重客户数；customer_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"event_customer_count":{"dtype":"Int64","unit":"count","meaning":"当前已表现 label=1 范围去重客户数","null":"unavailable; inspect status and report parameters"},"customer_coverage":{"dtype":"Float64","unit":"ratio","meaning":"customer_count / 同范围 base customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"customer_event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_customer_count / customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"customer_lift":{"dtype":"Float64","unit":"dimensionless","meaning":"customer_event_rate / 同范围 base customer_event_rate","null":"unavailable; inspect status and report parameters"},"event_rate_ci_lower":{"dtype":"Float64","unit":"ratio","meaning":"Wilson 事件率区间下界；confidence_level 见实际参数","null":"unavailable; inspect status and report parameters"},"event_rate_ci_upper":{"dtype":"Float64","unit":"ratio","meaning":"Wilson 事件率区间上界；confidence_level 见实际参数","null":"unavailable; inspect status and report parameters"},"lift_ci_lower":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率下界 / 同范围总体事件率；保守 Lift 下界","null":"unavailable; inspect status and report parameters"},"lift_ci_upper":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率上界 / 同范围总体事件率；保守 Lift 上界","null":"unavailable; inspect status and report parameters"},"p_value":{"dtype":"Float64","unit":"probability","meaning":"按 direction 的单侧事件富集检验 p 值；方法见 evaluator","null":"unavailable; inspect status and report parameters"},"q_value":{"dtype":"Float64","unit":"probability","meaning":"同数据范围、target、slice、group 候选检验族 BH 校正 q 值","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_relation":{"table":"rule_features","key":"rule_id","feature":"feature","roles":{"rule_id":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次"}},"feature_query":"relation"},"rule_explanations":{"rows":2,"grain":"final rule_id / rank / dataset / target / slice / group","schema_version":1,"fields":{"rank":{"dtype":"Int64","unit":"ordinal","meaning":"最终规则集的 1 起始顺序；cumulative 使用此前全部规则的并集","null":"unavailable; inspect status and report parameters"},"dataset":{"dtype":"String","unit":"dimension","meaning":"实际保存的 train/validation/in_sample 范围；不推断未保存的逐轮剩余样本统计","null":"unavailable; inspect status and report parameters"},"target":{"dtype":"String","unit":"identifier","meaning":"真实标签列 ID；各 target 独立排除未表现标签","null":"unavailable; inspect status and report parameters"},"slice":{"dtype":"String","unit":"dimension","meaning":"__overall__ 或 evaluator 实际构造的时间／客群切片值","null":"unavailable; inspect status and report parameters"},"group":{"dtype":"String","unit":"dimension","meaning":"hit / miss / total；此列不是原始客群，客群见 slice","null":"unavailable; inspect status and report parameters"},"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"expression":{"dtype":"String","unit":"definition","meaning":"既有 DSL 规范表达式；不执行报告文本","null":"unavailable; inspect status and report parameters"},"source":{"dtype":"String","unit":"category","meaning":"规则生成来源；不是业务特征来源","null":"unavailable; inspect status and report parameters"},"complexity":{"dtype":"Int64","unit":"count","meaning":"实际 complexity 整数计数；粒度见本表 grain","null":"unavailable; inspect status and report parameters"},"sample_count":{"dtype":"Int64","unit":"count","meaning":"当前 target 已表现样本数；group/slice/dataset 定义统计范围","null":"unavailable; inspect status and report parameters"},"event_count":{"dtype":"Int64","unit":"count","meaning":"当前范围已表现 label=1 样本数","null":"unavailable; inspect status and report parameters"},"coverage":{"dtype":"Float64","unit":"ratio","meaning":"当前范围 sample_count / 同 dataset、target、slice 的 base sample_count；只含已表现样本","null":"unavailable; inspect status and report parameters"},"event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_count / sample_count；零分母 null","null":"unavailable; inspect status and report parameters"},"lift":{"dtype":"Float64","unit":"dimensionless","meaning":"event_rate / 同 dataset、target、slice 的 base event_rate；零分母 null","null":"unavailable; inspect status and report parameters"},"lift_ci_lower":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率下界 / 同范围总体事件率；保守 Lift 下界","null":"unavailable; inspect status and report parameters"},"lift_ci_upper":{"dtype":"Float64","unit":"dimensionless","meaning":"规则 Wilson 事件率上界 / 同范围总体事件率；保守 Lift 上界","null":"unavailable; inspect status and report parameters"},"p_value":{"dtype":"Float64","unit":"probability","meaning":"按 direction 的单侧事件富集检验 p 值；方法见 evaluator","null":"unavailable; inspect status and report parameters"},"q_value":{"dtype":"Float64","unit":"probability","meaning":"同数据范围、target、slice、group 候选检验族 BH 校正 q 值","null":"unavailable; inspect status and report parameters"},"qualification":{"dtype":"String","unit":"state","meaning":"计算时 RuleSet 资格；快照恢复不会重建部署资格","null":"unavailable; inspect status and report parameters"},"amount_total":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现样本金金额和；amount_col 未提供则 null；币种见 business_context","null":"unavailable; inspect status and report parameters"},"amount_event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_amount / amount_total；零分母 null","null":"unavailable; inspect status and report parameters"},"customer_count":{"dtype":"Int64","unit":"count","meaning":"当前已表现范围去重客户数；customer_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"customer_event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_customer_count / customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"explanation":{"dtype":"String","unit":"text","meaning":"当前行所引用验证范围的中文说明；缺指标显示 N/A","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_relation":{"table":"rule_features","key":"rule_id","feature":"feature","roles":{"rule_id":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次"}},"feature_query":"relation"},"rule_features":{"rows":10,"grain":"distinct rule_id / English feature; includes rejected candidates","schema_version":1,"fields":{"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"feature":{"dtype":"String","unit":"identifier","meaning":"AST 提取的英文输入特征 ID；中文名不替代此身份","null":"unavailable; inspect status and report parameters"}},"feature_roles":{"feature":"feature"},"state":"computed","feature_query":"direct"}}</t>
   </si>
   <si>
-    <t>{"mars_version":"0.0.28","source_project":"deimos-rule","source_commit":"e6714c5e795054e44f0c58ad7097668b4117b4a2","target":"bad30","aux_targets":["late60"],"features":["main_score","aux_score"],"validation_status":"independent","profile":"production","qualification":"temporally_validated","group_col":null,"time_col":"application_date","time_grain":"month","amount_col":"amount","customer_col":"sample_id","generation_errors":[],"generator_diagnostics":[],"generators":[],"elapsed_seconds":0.03267479999340139,"resolved_spec":{"profile":"production","direction":"high_risk","candidate_filter":{"conditions":[{"metric":"lift","operator":"&gt;=","value":1.2},{"metric":"event_count","operator":"&gt;=","value":3.0},{"metric":"coverage","operator":"&gt;=","value":0.01},{"metric":"coverage","operator":"&lt;=","value":0.5}],"targets":"primary","target_scope":"all","slice_pass_rate":null},"validation_filter":{"conditions":[{"metric":"lift","operator":"&gt;=","value":2.0},{"metric":"event_count","operator":"&gt;=","value":3.0},{"metric":"coverage","operator":"&gt;=","value":0.01},{"metric":"coverage","operator":"&lt;=","value":0.5}],"targets":"primary","target_scope":"all","slice_pass_rate":0.8},"grade_filters":{},"selection_strategy":"ranked","top_k":10,"max_candidates":100000,"iou_threshold":0.3,"batch_size":100,"iou_batch_size":512,"max_rounds":10,"random_state":42,"on_generator_error":"raise","confidence_level":0.95,"max_fdr":0.05,"min_time_slices":3},"validation_summary":{"profile":"production","qualification":"temporally_validated","validation_status":"independent","confidence_level":0.95,"max_fdr":0.05,"min_time_slices":3,"selected_count":2,"temporal_assessed":true,"minimum_time_slice_count":3,"minimum_time_slice_pass_rate":1.0},"slice_definition":{"kind":"time","column":"application_date","group_precedes_time":true,"overall_value":"__overall__"},"analysis_states":{"slices":"computed","interactions":"not_computed","cumulative":"not_computed","bootstrap":"not_computed"},"advanced_analysis":null}</t>
+    <t>{"mars_version":"0.0.28","source_project":"deimos-rule","source_commit":"e6714c5e795054e44f0c58ad7097668b4117b4a2","target":"bad30","aux_targets":["late60"],"features":["main_score","aux_score"],"validation_status":"independent","profile":"production","qualification":"temporally_validated","group_col":null,"time_col":"application_date","time_grain":"month","amount_col":"amount","customer_col":"sample_id","generation_errors":[],"generator_diagnostics":[],"generators":[],"elapsed_seconds":0.05286455899477005,"resolved_spec":{"profile":"production","direction":"high_risk","candidate_filter":{"conditions":[{"metric":"lift","operator":"&gt;=","value":1.2},{"metric":"event_count","operator":"&gt;=","value":3.0},{"metric":"coverage","operator":"&gt;=","value":0.01},{"metric":"coverage","operator":"&lt;=","value":0.5}],"targets":"primary","target_scope":"all","slice_pass_rate":null},"validation_filter":{"conditions":[{"metric":"lift","operator":"&gt;=","value":2.0},{"metric":"event_count","operator":"&gt;=","value":3.0},{"metric":"coverage","operator":"&gt;=","value":0.01},{"metric":"coverage","operator":"&lt;=","value":0.5}],"targets":"primary","target_scope":"all","slice_pass_rate":0.8},"grade_filters":{},"selection_strategy":"ranked","top_k":10,"max_candidates":100000,"iou_threshold":0.3,"batch_size":100,"iou_batch_size":512,"max_rounds":10,"random_state":42,"on_generator_error":"raise","confidence_level":0.95,"max_fdr":0.05,"min_time_slices":3},"validation_summary":{"profile":"production","qualification":"temporally_validated","validation_status":"independent","confidence_level":0.95,"max_fdr":0.05,"min_time_slices":3,"selected_count":2,"temporal_assessed":true,"minimum_time_slice_count":3,"minimum_time_slice_pass_rate":1.0},"slice_definition":{"kind":"time","column":"application_date","group_precedes_time":true,"overall_value":"__overall__"},"analysis_states":{"slices":"computed","interactions":"not_computed","cumulative":"not_computed","bootstrap":"not_computed"},"advanced_analysis":null}</t>
   </si>
   <si>
     <t>{"dataset_id":"synthetic-consumer-credit-20261001","computation":"rule","producer":"mars.rule.MarsRuleReport","mars_version":"0.0.28","origin_project":"deimos-rule"}</t>
@@ -1002,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1018,7 +1039,7 @@
         <v>149</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1026,7 +1047,7 @@
         <v>150</v>
       </c>
       <c r="B3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1034,7 +1055,7 @@
         <v>151</v>
       </c>
       <c r="B4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1042,7 +1063,7 @@
         <v>152</v>
       </c>
       <c r="B5" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1050,7 +1071,7 @@
         <v>153</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1058,7 +1079,7 @@
         <v>154</v>
       </c>
       <c r="B7" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1066,7 +1087,7 @@
         <v>155</v>
       </c>
       <c r="B8" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1074,7 +1095,7 @@
         <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1082,7 +1103,7 @@
         <v>156</v>
       </c>
       <c r="B10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1090,7 +1111,7 @@
         <v>157</v>
       </c>
       <c r="B11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1098,7 +1119,7 @@
         <v>158</v>
       </c>
       <c r="B12" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1106,31 +1127,63 @@
         <v>159</v>
       </c>
       <c r="B13" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>160</v>
+        <v>102</v>
       </c>
       <c r="B14" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B15" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
         <v>162</v>
       </c>
-      <c r="B16" t="s">
-        <v>176</v>
+      <c r="B17" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>163</v>
+      </c>
+      <c r="B18" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B19" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B20" t="s">
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -1153,42 +1206,42 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B3" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B5" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B6" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1196,12 +1249,12 @@
         <v>55</v>
       </c>
       <c r="B7" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B8" t="s">
         <v>46</v>
@@ -1209,42 +1262,42 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B9" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B10" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B11" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B12" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B13" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -1650,13 +1703,13 @@
         <v>98</v>
       </c>
       <c r="Q2">
-        <v>4.615813933430166E-54</v>
+        <v>1.308682289566425E-55</v>
       </c>
       <c r="R2">
-        <v>2.97607241221415</v>
+        <v>3.035082055020192</v>
       </c>
       <c r="S2">
-        <v>3.550170066569011</v>
+        <v>3.614024477046496</v>
       </c>
       <c r="T2" t="b">
         <v>1</v>
@@ -1715,13 +1768,13 @@
         <v>98</v>
       </c>
       <c r="Q3">
-        <v>1.512109494013924E-29</v>
+        <v>2.846919799698625E-29</v>
       </c>
       <c r="R3">
-        <v>2.268117517598033</v>
+        <v>2.273372818285476</v>
       </c>
       <c r="S3">
-        <v>2.812798503446889</v>
+        <v>2.823085511198407</v>
       </c>
       <c r="T3" t="b">
         <v>1</v>
@@ -1821,13 +1874,13 @@
         <v>98</v>
       </c>
       <c r="Q5">
-        <v>1.966419192521019E-09</v>
+        <v>1.419839033872502E-09</v>
       </c>
       <c r="R5">
-        <v>1.504949067392025</v>
+        <v>1.513224650634103</v>
       </c>
       <c r="S5">
-        <v>1.981911776638136</v>
+        <v>1.992247398407267</v>
       </c>
       <c r="T5" t="b">
         <v>1</v>
@@ -1990,49 +2043,49 @@
         <v>125</v>
       </c>
       <c r="F2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H2">
-        <v>0.06348630509704335</v>
+        <v>0.06312352621077454</v>
       </c>
       <c r="I2">
-        <v>0.52</v>
+        <v>0.5201149425287356</v>
       </c>
       <c r="J2">
-        <v>3.400664294187426</v>
+        <v>3.401415988328492</v>
       </c>
       <c r="K2">
-        <v>5268109.347199009</v>
+        <v>5223220.34613738</v>
       </c>
       <c r="L2">
-        <v>2696051.917113932</v>
+        <v>2676066.727887406</v>
       </c>
       <c r="M2">
-        <v>0.06005704650049617</v>
+        <v>0.0595453067763478</v>
       </c>
       <c r="N2">
-        <v>0.5117684048352927</v>
+        <v>0.5123403859204183</v>
       </c>
       <c r="O2">
-        <v>3.384830114613531</v>
+        <v>3.38861319067612</v>
       </c>
       <c r="P2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="Q2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="R2">
-        <v>0.06348630509704335</v>
+        <v>0.06312352621077454</v>
       </c>
       <c r="S2">
-        <v>0.52</v>
+        <v>0.5201149425287356</v>
       </c>
       <c r="T2">
-        <v>3.400664294187426</v>
+        <v>3.401415988328492</v>
       </c>
     </row>
     <row r="3" spans="1:26">
@@ -2052,49 +2105,49 @@
         <v>126</v>
       </c>
       <c r="F3">
-        <v>5163</v>
+        <v>5165</v>
       </c>
       <c r="G3">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H3">
-        <v>0.9365136949029567</v>
+        <v>0.9368764737892255</v>
       </c>
       <c r="I3">
-        <v>0.1280263412744528</v>
+        <v>0.1281703775411423</v>
       </c>
       <c r="J3">
-        <v>0.837258860552857</v>
+        <v>0.8382008201474703</v>
       </c>
       <c r="K3">
-        <v>82450312.62274395</v>
+        <v>82495201.62380558</v>
       </c>
       <c r="L3">
-        <v>10566509.3832048</v>
+        <v>10586494.57243132</v>
       </c>
       <c r="M3">
-        <v>0.9399429534995039</v>
+        <v>0.9404546932236523</v>
       </c>
       <c r="N3">
-        <v>0.1281560863395686</v>
+        <v>0.1283286101985401</v>
       </c>
       <c r="O3">
-        <v>0.8476228237512887</v>
+        <v>0.8487638944930903</v>
       </c>
       <c r="P3">
-        <v>5163</v>
+        <v>5165</v>
       </c>
       <c r="Q3">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="R3">
-        <v>0.9365136949029567</v>
+        <v>0.9368764737892255</v>
       </c>
       <c r="S3">
-        <v>0.1280263412744528</v>
+        <v>0.1281703775411423</v>
       </c>
       <c r="T3">
-        <v>0.837258860552857</v>
+        <v>0.8382008201474703</v>
       </c>
     </row>
     <row r="4" spans="1:26">
@@ -2138,7 +2191,7 @@
         <v>1</v>
       </c>
       <c r="N4">
-        <v>0.1511947091896294</v>
+        <v>0.1511947091896295</v>
       </c>
       <c r="O4">
         <v>1</v>
@@ -2176,49 +2229,49 @@
         <v>125</v>
       </c>
       <c r="F5">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="G5">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H5">
-        <v>0.06457464175584982</v>
+        <v>0.06330491565390894</v>
       </c>
       <c r="I5">
-        <v>0.3792134831460674</v>
+        <v>0.3839541547277937</v>
       </c>
       <c r="J5">
-        <v>2.479957215402455</v>
+        <v>2.510959970361004</v>
       </c>
       <c r="K5">
-        <v>5744589.98282891</v>
+        <v>5566957.631956978</v>
       </c>
       <c r="L5">
-        <v>2276468.803239466</v>
+        <v>2246857.94361996</v>
       </c>
       <c r="M5">
-        <v>0.06548898000920851</v>
+        <v>0.06346395098015462</v>
       </c>
       <c r="N5">
-        <v>0.3962804673691305</v>
+        <v>0.4036060793281287</v>
       </c>
       <c r="O5">
-        <v>2.620994276143042</v>
+        <v>2.669445786108316</v>
       </c>
       <c r="P5">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="Q5">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R5">
-        <v>0.06457464175584982</v>
+        <v>0.06330491565390894</v>
       </c>
       <c r="S5">
-        <v>0.3792134831460674</v>
+        <v>0.3839541547277937</v>
       </c>
       <c r="T5">
-        <v>2.479957215402455</v>
+        <v>2.510959970361004</v>
       </c>
     </row>
     <row r="6" spans="1:26">
@@ -2238,49 +2291,49 @@
         <v>126</v>
       </c>
       <c r="F6">
-        <v>5157</v>
+        <v>5164</v>
       </c>
       <c r="G6">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H6">
-        <v>0.9354253582441502</v>
+        <v>0.9366950843460911</v>
       </c>
       <c r="I6">
-        <v>0.1372891215823153</v>
+        <v>0.1372966692486444</v>
       </c>
       <c r="J6">
-        <v>0.8978350264333382</v>
+        <v>0.897884386201396</v>
       </c>
       <c r="K6">
-        <v>81973831.98711406</v>
+        <v>82151464.33798599</v>
       </c>
       <c r="L6">
-        <v>10986092.49707926</v>
+        <v>11015703.35669877</v>
       </c>
       <c r="M6">
-        <v>0.9345110199907916</v>
+        <v>0.9365360490198456</v>
       </c>
       <c r="N6">
-        <v>0.1340195063566899</v>
+        <v>0.1340901643746503</v>
       </c>
       <c r="O6">
-        <v>0.8864034136842828</v>
+        <v>0.8868707449708012</v>
       </c>
       <c r="P6">
-        <v>5157</v>
+        <v>5164</v>
       </c>
       <c r="Q6">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="R6">
-        <v>0.9354253582441502</v>
+        <v>0.9366950843460911</v>
       </c>
       <c r="S6">
-        <v>0.1372891215823153</v>
+        <v>0.1372966692486444</v>
       </c>
       <c r="T6">
-        <v>0.8978350264333382</v>
+        <v>0.897884386201396</v>
       </c>
     </row>
     <row r="7" spans="1:26">
@@ -2324,7 +2377,7 @@
         <v>1</v>
       </c>
       <c r="N7">
-        <v>0.1511947091896294</v>
+        <v>0.1511947091896295</v>
       </c>
       <c r="O7">
         <v>1</v>
@@ -2377,7 +2430,7 @@
         <v>0.05511016034227677</v>
       </c>
       <c r="K8">
-        <v>5581092.918251459</v>
+        <v>5581092.91825146</v>
       </c>
       <c r="L8">
         <v>49774.88909300734</v>
@@ -2386,10 +2439,10 @@
         <v>0.06362509485366531</v>
       </c>
       <c r="N8">
-        <v>0.008918484214844728</v>
+        <v>0.008918484214844726</v>
       </c>
       <c r="O8">
-        <v>0.05898674803269145</v>
+        <v>0.05898674803269142</v>
       </c>
       <c r="P8">
         <v>356</v>
@@ -2510,7 +2563,7 @@
         <v>1</v>
       </c>
       <c r="N10">
-        <v>0.1511947091896294</v>
+        <v>0.1511947091896295</v>
       </c>
       <c r="O10">
         <v>1</v>
@@ -2548,49 +2601,49 @@
         <v>125</v>
       </c>
       <c r="F11">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="G11">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H11">
-        <v>0.0567748957010702</v>
+        <v>0.05568655904226374</v>
       </c>
       <c r="I11">
-        <v>0.2204472843450479</v>
+        <v>0.2182410423452769</v>
       </c>
       <c r="J11">
-        <v>1.441667708889975</v>
+        <v>1.42723946198044</v>
       </c>
       <c r="K11">
-        <v>5061452.717791138</v>
+        <v>4977420.147203127</v>
       </c>
       <c r="L11">
-        <v>1147278.187689293</v>
+        <v>1109407.544913301</v>
       </c>
       <c r="M11">
-        <v>0.05770113739079191</v>
+        <v>0.05674315651629778</v>
       </c>
       <c r="N11">
-        <v>0.2266697431859001</v>
+        <v>0.2228880649218834</v>
       </c>
       <c r="O11">
-        <v>1.499190973022802</v>
+        <v>1.474178998170734</v>
       </c>
       <c r="P11">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="Q11">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="R11">
-        <v>0.0567748957010702</v>
+        <v>0.05568655904226374</v>
       </c>
       <c r="S11">
-        <v>0.2204472843450479</v>
+        <v>0.2182410423452769</v>
       </c>
       <c r="T11">
-        <v>1.441667708889975</v>
+        <v>1.42723946198044</v>
       </c>
     </row>
     <row r="12" spans="1:26">
@@ -2610,49 +2663,49 @@
         <v>126</v>
       </c>
       <c r="F12">
-        <v>5200</v>
+        <v>5206</v>
       </c>
       <c r="G12">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="H12">
-        <v>0.9432251042989298</v>
+        <v>0.9443134409577363</v>
       </c>
       <c r="I12">
-        <v>0.1488461538461539</v>
+        <v>0.149058778332693</v>
       </c>
       <c r="J12">
-        <v>0.9734150013687379</v>
+        <v>0.9748055100215145</v>
       </c>
       <c r="K12">
-        <v>82656969.25215183</v>
+        <v>82741001.82273984</v>
       </c>
       <c r="L12">
-        <v>12115283.11262943</v>
+        <v>12153153.75540543</v>
       </c>
       <c r="M12">
-        <v>0.9422988626092083</v>
+        <v>0.9432568434837023</v>
       </c>
       <c r="N12">
-        <v>0.1465730382113428</v>
+        <v>0.1468818782426847</v>
       </c>
       <c r="O12">
-        <v>0.9694323233725718</v>
+        <v>0.9714749876496301</v>
       </c>
       <c r="P12">
-        <v>5200</v>
+        <v>5206</v>
       </c>
       <c r="Q12">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="R12">
-        <v>0.9432251042989298</v>
+        <v>0.9443134409577363</v>
       </c>
       <c r="S12">
-        <v>0.1488461538461539</v>
+        <v>0.149058778332693</v>
       </c>
       <c r="T12">
-        <v>0.9734150013687379</v>
+        <v>0.9748055100215145</v>
       </c>
     </row>
     <row r="13" spans="1:26">
@@ -2696,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="N13">
-        <v>0.1511947091896294</v>
+        <v>0.1511947091896295</v>
       </c>
       <c r="O13">
         <v>1</v>
@@ -2802,7 +2855,7 @@
         <v>1</v>
       </c>
       <c r="N15">
-        <v>0.1511947091896294</v>
+        <v>0.1511947091896295</v>
       </c>
       <c r="O15">
         <v>1</v>
@@ -2864,7 +2917,7 @@
         <v>1</v>
       </c>
       <c r="N16">
-        <v>0.1511947091896294</v>
+        <v>0.1511947091896295</v>
       </c>
       <c r="O16">
         <v>1</v>
@@ -2902,49 +2955,49 @@
         <v>125</v>
       </c>
       <c r="F17">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G17">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H17">
-        <v>0.06864796986186689</v>
+        <v>0.06822938467978233</v>
       </c>
       <c r="I17">
-        <v>0.4695121951219512</v>
+        <v>0.4693251533742331</v>
       </c>
       <c r="J17">
-        <v>3.094247266610597</v>
+        <v>3.09301459699598</v>
       </c>
       <c r="K17">
-        <v>4995440.983244665</v>
+        <v>4968327.833791792</v>
       </c>
       <c r="L17">
-        <v>2164438.604517097</v>
+        <v>2139534.792681993</v>
       </c>
       <c r="M17">
-        <v>0.06537358984430942</v>
+        <v>0.06501876953561903</v>
       </c>
       <c r="N17">
-        <v>0.433282789602939</v>
+        <v>0.4306347858388232</v>
       </c>
       <c r="O17">
-        <v>2.942776975836494</v>
+        <v>2.924792221546785</v>
       </c>
       <c r="P17">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="Q17">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="R17">
-        <v>0.06864796986186689</v>
+        <v>0.06822938467978233</v>
       </c>
       <c r="S17">
-        <v>0.4695121951219512</v>
+        <v>0.4693251533742331</v>
       </c>
       <c r="T17">
-        <v>3.094247266610597</v>
+        <v>3.09301459699598</v>
       </c>
     </row>
     <row r="18" spans="1:26">
@@ -2964,49 +3017,49 @@
         <v>126</v>
       </c>
       <c r="F18">
-        <v>4450</v>
+        <v>4452</v>
       </c>
       <c r="G18">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H18">
-        <v>0.9313520301381331</v>
+        <v>0.9317706153202177</v>
       </c>
       <c r="I18">
-        <v>0.128314606741573</v>
+        <v>0.12848158131177</v>
       </c>
       <c r="J18">
-        <v>0.845637504843084</v>
+        <v>0.8467379248381199</v>
       </c>
       <c r="K18">
-        <v>71418306.45117901</v>
+        <v>71445419.60063188</v>
       </c>
       <c r="L18">
-        <v>9086417.958607342</v>
+        <v>9111321.770442449</v>
       </c>
       <c r="M18">
-        <v>0.9346264101556907</v>
+        <v>0.934981230464381</v>
       </c>
       <c r="N18">
-        <v>0.1272281353355634</v>
+        <v>0.1275284240945499</v>
       </c>
       <c r="O18">
-        <v>0.8641100831334884</v>
+        <v>0.866149589126463</v>
       </c>
       <c r="P18">
-        <v>4450</v>
+        <v>4452</v>
       </c>
       <c r="Q18">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="R18">
-        <v>0.9313520301381331</v>
+        <v>0.9317706153202177</v>
       </c>
       <c r="S18">
-        <v>0.128314606741573</v>
+        <v>0.12848158131177</v>
       </c>
       <c r="T18">
-        <v>0.845637504843084</v>
+        <v>0.8467379248381199</v>
       </c>
     </row>
     <row r="19" spans="1:26">
@@ -3088,49 +3141,49 @@
         <v>125</v>
       </c>
       <c r="F20">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="G20">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H20">
-        <v>0.06236919213059858</v>
+        <v>0.06090414399330264</v>
       </c>
       <c r="I20">
-        <v>0.3557046979865772</v>
+        <v>0.3608247422680412</v>
       </c>
       <c r="J20">
-        <v>2.344216616523953</v>
+        <v>2.377959473871312</v>
       </c>
       <c r="K20">
-        <v>4740880.346931658</v>
+        <v>4563247.996059727</v>
       </c>
       <c r="L20">
-        <v>1748343.91684742</v>
+        <v>1718733.057227914</v>
       </c>
       <c r="M20">
-        <v>0.06204224378604335</v>
+        <v>0.05971763130679843</v>
       </c>
       <c r="N20">
-        <v>0.3687804350470403</v>
+        <v>0.376646866160245</v>
       </c>
       <c r="O20">
-        <v>2.50468885318503</v>
+        <v>2.558116205753445</v>
       </c>
       <c r="P20">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="Q20">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="R20">
-        <v>0.06236919213059858</v>
+        <v>0.06090414399330264</v>
       </c>
       <c r="S20">
-        <v>0.3557046979865772</v>
+        <v>0.3608247422680412</v>
       </c>
       <c r="T20">
-        <v>2.344216616523953</v>
+        <v>2.377959473871312</v>
       </c>
     </row>
     <row r="21" spans="1:26">
@@ -3150,49 +3203,49 @@
         <v>126</v>
       </c>
       <c r="F21">
-        <v>4480</v>
+        <v>4487</v>
       </c>
       <c r="G21">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H21">
-        <v>0.9376308078694015</v>
+        <v>0.9390958560066973</v>
       </c>
       <c r="I21">
-        <v>0.1381696428571429</v>
+        <v>0.1381769556496546</v>
       </c>
       <c r="J21">
-        <v>0.910585591133005</v>
+        <v>0.9106337849573096</v>
       </c>
       <c r="K21">
-        <v>71672867.08749202</v>
+        <v>71850499.43836394</v>
       </c>
       <c r="L21">
-        <v>9502512.64627702</v>
+        <v>9532123.505896525</v>
       </c>
       <c r="M21">
-        <v>0.9379577562139567</v>
+        <v>0.9402823686932015</v>
       </c>
       <c r="N21">
-        <v>0.1325817290757627</v>
+        <v>0.1326660716405116</v>
       </c>
       <c r="O21">
-        <v>0.9004707066677821</v>
+        <v>0.9010435458471394</v>
       </c>
       <c r="P21">
-        <v>4480</v>
+        <v>4487</v>
       </c>
       <c r="Q21">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="R21">
-        <v>0.9376308078694015</v>
+        <v>0.9390958560066973</v>
       </c>
       <c r="S21">
-        <v>0.1381696428571429</v>
+        <v>0.1381769556496546</v>
       </c>
       <c r="T21">
-        <v>0.910585591133005</v>
+        <v>0.9106337849573096</v>
       </c>
     </row>
     <row r="22" spans="1:26">
@@ -3351,13 +3404,13 @@
         <v>1.06595510298542</v>
       </c>
       <c r="K24">
-        <v>71573924.58484586</v>
+        <v>71573924.58484584</v>
       </c>
       <c r="L24">
         <v>11202581.10564446</v>
       </c>
       <c r="M24">
-        <v>0.9366629302700901</v>
+        <v>0.93666293027009</v>
       </c>
       <c r="N24">
         <v>0.1565176308358582</v>
@@ -3460,49 +3513,49 @@
         <v>125</v>
       </c>
       <c r="F26">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="G26">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H26">
-        <v>0.05692758476349937</v>
+        <v>0.05567182921724571</v>
       </c>
       <c r="I26">
-        <v>0.1875</v>
+        <v>0.1879699248120301</v>
       </c>
       <c r="J26">
-        <v>1.235689655172414</v>
+        <v>1.23878662172673</v>
       </c>
       <c r="K26">
-        <v>4410187.397475898</v>
+        <v>4326154.826887889</v>
       </c>
       <c r="L26">
-        <v>837628.9484530159</v>
+        <v>829171.7227178847</v>
       </c>
       <c r="M26">
-        <v>0.05771458075996873</v>
+        <v>0.05661487588474161</v>
       </c>
       <c r="N26">
-        <v>0.1899304662047739</v>
+        <v>0.1916648284440543</v>
       </c>
       <c r="O26">
-        <v>1.289972776138877</v>
+        <v>1.301752245316943</v>
       </c>
       <c r="P26">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="Q26">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R26">
-        <v>0.05692758476349937</v>
+        <v>0.05567182921724571</v>
       </c>
       <c r="S26">
-        <v>0.1875</v>
+        <v>0.1879699248120301</v>
       </c>
       <c r="T26">
-        <v>1.235689655172414</v>
+        <v>1.23878662172673</v>
       </c>
     </row>
     <row r="27" spans="1:26">
@@ -3522,49 +3575,49 @@
         <v>126</v>
       </c>
       <c r="F27">
-        <v>4506</v>
+        <v>4512</v>
       </c>
       <c r="G27">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H27">
-        <v>0.9430724152365006</v>
+        <v>0.9443281707827543</v>
       </c>
       <c r="I27">
-        <v>0.1495783399911229</v>
+        <v>0.1496010638297872</v>
       </c>
       <c r="J27">
-        <v>0.985772839279428</v>
+        <v>0.9859225972120323</v>
       </c>
       <c r="K27">
-        <v>72003560.03694777</v>
+        <v>72087592.60753578</v>
       </c>
       <c r="L27">
-        <v>10413227.61467142</v>
+        <v>10421684.84040656</v>
       </c>
       <c r="M27">
-        <v>0.9422854192400313</v>
+        <v>0.9433851241152583</v>
       </c>
       <c r="N27">
-        <v>0.1446210105351458</v>
+        <v>0.1445697444377843</v>
       </c>
       <c r="O27">
-        <v>0.9822392909144692</v>
+        <v>0.9818911010149937</v>
       </c>
       <c r="P27">
-        <v>4506</v>
+        <v>4512</v>
       </c>
       <c r="Q27">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="R27">
-        <v>0.9430724152365006</v>
+        <v>0.9443281707827543</v>
       </c>
       <c r="S27">
-        <v>0.1495783399911229</v>
+        <v>0.1496010638297872</v>
       </c>
       <c r="T27">
-        <v>0.985772839279428</v>
+        <v>0.9859225972120323</v>
       </c>
     </row>
     <row r="28" spans="1:26">
@@ -3814,67 +3867,67 @@
         <v>125</v>
       </c>
       <c r="F32">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="G32">
         <v>167</v>
       </c>
       <c r="H32">
-        <v>0.05800756620428751</v>
+        <v>0.05692667987749955</v>
       </c>
       <c r="I32">
-        <v>0.5186335403726708</v>
+        <v>0.5284810126582279</v>
       </c>
       <c r="J32">
-        <v>3.26409839298038</v>
+        <v>3.326074944745831</v>
       </c>
       <c r="K32">
-        <v>5276321.036114124</v>
+        <v>5195547.6394781</v>
       </c>
       <c r="L32">
-        <v>2722210.04314496</v>
+        <v>2722210.043144961</v>
       </c>
       <c r="M32">
-        <v>0.05958380927934762</v>
+        <v>0.0586716610936962</v>
       </c>
       <c r="N32">
-        <v>0.5159295699622173</v>
+        <v>0.5239505499786756</v>
       </c>
       <c r="O32">
-        <v>3.198493655810592</v>
+        <v>3.248219539321989</v>
       </c>
       <c r="P32">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="Q32">
         <v>167</v>
       </c>
       <c r="R32">
-        <v>0.05800756620428751</v>
+        <v>0.05692667987749955</v>
       </c>
       <c r="S32">
-        <v>0.5186335403726708</v>
+        <v>0.5284810126582279</v>
       </c>
       <c r="T32">
-        <v>3.26409839298038</v>
+        <v>3.326074944745831</v>
       </c>
       <c r="U32">
-        <v>0.4728690087502938</v>
+        <v>0.4822450680107745</v>
       </c>
       <c r="V32">
-        <v>0.5640875515607761</v>
+        <v>0.5742333973617384</v>
       </c>
       <c r="W32">
-        <v>2.97607241221415</v>
+        <v>3.035082055020192</v>
       </c>
       <c r="X32">
-        <v>3.550170066569011</v>
+        <v>3.614024477046496</v>
       </c>
       <c r="Y32">
-        <v>1.538604644476722E-54</v>
+        <v>4.362274298554751E-56</v>
       </c>
       <c r="Z32">
-        <v>4.615813933430166E-54</v>
+        <v>1.308682289566425E-55</v>
       </c>
     </row>
     <row r="33" spans="1:26">
@@ -3894,49 +3947,49 @@
         <v>126</v>
       </c>
       <c r="F33">
-        <v>5229</v>
+        <v>5235</v>
       </c>
       <c r="G33">
         <v>715</v>
       </c>
       <c r="H33">
-        <v>0.9419924337957125</v>
+        <v>0.9430733201225004</v>
       </c>
       <c r="I33">
-        <v>0.1367374258940524</v>
+        <v>0.1365807067812798</v>
       </c>
       <c r="J33">
-        <v>0.8605776089998695</v>
+        <v>0.8595912736313881</v>
       </c>
       <c r="K33">
-        <v>83276611.37841266</v>
+        <v>83357384.77504869</v>
       </c>
       <c r="L33">
         <v>11561725.22635978</v>
       </c>
       <c r="M33">
-        <v>0.9404161907206525</v>
+        <v>0.9413283389063037</v>
       </c>
       <c r="N33">
-        <v>0.1388352027656695</v>
+        <v>0.1387006713029767</v>
       </c>
       <c r="O33">
-        <v>0.8607056875644691</v>
+        <v>0.8598716628157786</v>
       </c>
       <c r="P33">
-        <v>5229</v>
+        <v>5235</v>
       </c>
       <c r="Q33">
         <v>715</v>
       </c>
       <c r="R33">
-        <v>0.9419924337957125</v>
+        <v>0.9430733201225004</v>
       </c>
       <c r="S33">
-        <v>0.1367374258940524</v>
+        <v>0.1365807067812798</v>
       </c>
       <c r="T33">
-        <v>0.8605776089998695</v>
+        <v>0.8595912736313881</v>
       </c>
     </row>
     <row r="34" spans="1:26">
@@ -3971,16 +4024,16 @@
         <v>1</v>
       </c>
       <c r="K34">
-        <v>88552932.41452678</v>
+        <v>88552932.41452679</v>
       </c>
       <c r="L34">
-        <v>14283935.26950475</v>
+        <v>14283935.26950474</v>
       </c>
       <c r="M34">
         <v>1</v>
       </c>
       <c r="N34">
-        <v>0.161303921621025</v>
+        <v>0.1613039216210249</v>
       </c>
       <c r="O34">
         <v>1</v>
@@ -4018,67 +4071,67 @@
         <v>125</v>
       </c>
       <c r="F35">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="G35">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H35">
-        <v>0.06215096379030805</v>
+        <v>0.06107007746352008</v>
       </c>
       <c r="I35">
-        <v>0.4028985507246377</v>
+        <v>0.4041297935103245</v>
       </c>
       <c r="J35">
-        <v>2.53570278352887</v>
+        <v>2.543451795664185</v>
       </c>
       <c r="K35">
-        <v>5599237.991291957</v>
+        <v>5512696.924044427</v>
       </c>
       <c r="L35">
-        <v>2330073.762254959</v>
+        <v>2316168.973155275</v>
       </c>
       <c r="M35">
-        <v>0.06323040738031419</v>
+        <v>0.0622531267314654</v>
       </c>
       <c r="N35">
-        <v>0.4161412259808807</v>
+        <v>0.420151697992496</v>
       </c>
       <c r="O35">
-        <v>2.579858082797159</v>
+        <v>2.604720912983259</v>
       </c>
       <c r="P35">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="Q35">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="R35">
-        <v>0.06215096379030805</v>
+        <v>0.06107007746352008</v>
       </c>
       <c r="S35">
-        <v>0.4028985507246377</v>
+        <v>0.4041297935103245</v>
       </c>
       <c r="T35">
-        <v>2.53570278352887</v>
+        <v>2.543451795664185</v>
       </c>
       <c r="U35">
-        <v>0.3603818502110368</v>
+        <v>0.3612168664615006</v>
       </c>
       <c r="V35">
-        <v>0.4469263700306533</v>
+        <v>0.4485608756759135</v>
       </c>
       <c r="W35">
-        <v>2.268117517598033</v>
+        <v>2.273372818285476</v>
       </c>
       <c r="X35">
-        <v>2.812798503446889</v>
+        <v>2.823085511198407</v>
       </c>
       <c r="Y35">
-        <v>1.008072996009283E-29</v>
+        <v>1.897946533132417E-29</v>
       </c>
       <c r="Z35">
-        <v>1.512109494013924E-29</v>
+        <v>2.846919799698625E-29</v>
       </c>
     </row>
     <row r="36" spans="1:26">
@@ -4098,49 +4151,49 @@
         <v>126</v>
       </c>
       <c r="F36">
-        <v>5206</v>
+        <v>5212</v>
       </c>
       <c r="G36">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="H36">
-        <v>0.937849036209692</v>
+        <v>0.9389299225364799</v>
       </c>
       <c r="I36">
-        <v>0.1427199385324625</v>
+        <v>0.1429393706830391</v>
       </c>
       <c r="J36">
-        <v>0.8982294544146253</v>
+        <v>0.8996104837432541</v>
       </c>
       <c r="K36">
-        <v>82953694.42323484</v>
+        <v>83040235.49048236</v>
       </c>
       <c r="L36">
-        <v>11953861.50724979</v>
+        <v>11967766.29634947</v>
       </c>
       <c r="M36">
-        <v>0.936769592619686</v>
+        <v>0.9377468732685346</v>
       </c>
       <c r="N36">
-        <v>0.1441028225489326</v>
+        <v>0.1441200910096306</v>
       </c>
       <c r="O36">
-        <v>0.8933621768198206</v>
+        <v>0.8934692322498715</v>
       </c>
       <c r="P36">
-        <v>5206</v>
+        <v>5212</v>
       </c>
       <c r="Q36">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="R36">
-        <v>0.937849036209692</v>
+        <v>0.9389299225364799</v>
       </c>
       <c r="S36">
-        <v>0.1427199385324625</v>
+        <v>0.1429393706830391</v>
       </c>
       <c r="T36">
-        <v>0.8982294544146253</v>
+        <v>0.8996104837432541</v>
       </c>
     </row>
     <row r="37" spans="1:26">
@@ -4175,16 +4228,16 @@
         <v>1</v>
       </c>
       <c r="K37">
-        <v>88552932.41452678</v>
+        <v>88552932.41452679</v>
       </c>
       <c r="L37">
-        <v>14283935.26950475</v>
+        <v>14283935.26950474</v>
       </c>
       <c r="M37">
         <v>1</v>
       </c>
       <c r="N37">
-        <v>0.161303921621025</v>
+        <v>0.1613039216210249</v>
       </c>
       <c r="O37">
         <v>1</v>
@@ -4222,67 +4275,67 @@
         <v>125</v>
       </c>
       <c r="F38">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G38">
         <v>103</v>
       </c>
       <c r="H38">
-        <v>0.06737524770311655</v>
+        <v>0.0670149522608539</v>
       </c>
       <c r="I38">
-        <v>0.2754010695187166</v>
+        <v>0.2768817204301075</v>
       </c>
       <c r="J38">
-        <v>1.733278159748748</v>
+        <v>1.742596859532343</v>
       </c>
       <c r="K38">
-        <v>5790362.738086015</v>
+        <v>5761686.391226349</v>
       </c>
       <c r="L38">
         <v>1599392.987598401</v>
       </c>
       <c r="M38">
-        <v>0.06538871813957149</v>
+        <v>0.06506488530786549</v>
       </c>
       <c r="N38">
-        <v>0.2762163719171547</v>
+        <v>0.2775911215913952</v>
       </c>
       <c r="O38">
-        <v>1.712397126748787</v>
+        <v>1.720919856143244</v>
       </c>
       <c r="P38">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="Q38">
         <v>103</v>
       </c>
       <c r="R38">
-        <v>0.06737524770311655</v>
+        <v>0.0670149522608539</v>
       </c>
       <c r="S38">
-        <v>0.2754010695187166</v>
+        <v>0.2768817204301075</v>
       </c>
       <c r="T38">
-        <v>1.733278159748748</v>
+        <v>1.742596859532343</v>
       </c>
       <c r="U38">
-        <v>0.2391217938100821</v>
+        <v>0.2404367036316481</v>
       </c>
       <c r="V38">
-        <v>0.3149065370194265</v>
+        <v>0.316548766960045</v>
       </c>
       <c r="W38">
-        <v>1.504949067392025</v>
+        <v>1.513224650634103</v>
       </c>
       <c r="X38">
-        <v>1.981911776638136</v>
+        <v>1.992247398407267</v>
       </c>
       <c r="Y38">
-        <v>1.966419192521019E-09</v>
+        <v>1.419839033872502E-09</v>
       </c>
       <c r="Z38">
-        <v>1.966419192521019E-09</v>
+        <v>1.419839033872502E-09</v>
       </c>
     </row>
     <row r="39" spans="1:26">
@@ -4302,49 +4355,49 @@
         <v>126</v>
       </c>
       <c r="F39">
-        <v>5177</v>
+        <v>5179</v>
       </c>
       <c r="G39">
         <v>779</v>
       </c>
       <c r="H39">
-        <v>0.9326247522968835</v>
+        <v>0.9329850477391461</v>
       </c>
       <c r="I39">
-        <v>0.1504732470542785</v>
+        <v>0.1504151380575401</v>
       </c>
       <c r="J39">
-        <v>0.9470260707463719</v>
+        <v>0.9466603530129306</v>
       </c>
       <c r="K39">
-        <v>82762569.67644076</v>
+        <v>82791246.02330044</v>
       </c>
       <c r="L39">
         <v>12684542.28190635</v>
       </c>
       <c r="M39">
-        <v>0.9346112818604285</v>
+        <v>0.9349351146921345</v>
       </c>
       <c r="N39">
-        <v>0.1532642392750298</v>
+        <v>0.1532111532460383</v>
       </c>
       <c r="O39">
-        <v>0.950158171821241</v>
+        <v>0.9498290661897231</v>
       </c>
       <c r="P39">
-        <v>5177</v>
+        <v>5179</v>
       </c>
       <c r="Q39">
         <v>779</v>
       </c>
       <c r="R39">
-        <v>0.9326247522968835</v>
+        <v>0.9329850477391461</v>
       </c>
       <c r="S39">
-        <v>0.1504732470542785</v>
+        <v>0.1504151380575401</v>
       </c>
       <c r="T39">
-        <v>0.9470260707463719</v>
+        <v>0.9466603530129306</v>
       </c>
     </row>
     <row r="40" spans="1:26">
@@ -4379,16 +4432,16 @@
         <v>1</v>
       </c>
       <c r="K40">
-        <v>88552932.41452678</v>
+        <v>88552932.41452679</v>
       </c>
       <c r="L40">
-        <v>14283935.26950475</v>
+        <v>14283935.26950474</v>
       </c>
       <c r="M40">
         <v>1</v>
       </c>
       <c r="N40">
-        <v>0.161303921621025</v>
+        <v>0.1613039216210249</v>
       </c>
       <c r="O40">
         <v>1</v>
@@ -4426,67 +4479,67 @@
         <v>125</v>
       </c>
       <c r="F41">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="G41">
         <v>138</v>
       </c>
       <c r="H41">
-        <v>0.05816368923971749</v>
+        <v>0.05712505193186539</v>
       </c>
       <c r="I41">
-        <v>0.4928571428571429</v>
+        <v>0.5018181818181818</v>
       </c>
       <c r="J41">
-        <v>3.250156555772994</v>
+        <v>3.309250311332503</v>
       </c>
       <c r="K41">
-        <v>4624977.744734897</v>
+        <v>4564210.834527904</v>
       </c>
       <c r="L41">
         <v>2295916.928902857</v>
       </c>
       <c r="M41">
-        <v>0.06002696793015173</v>
+        <v>0.05923828232526161</v>
       </c>
       <c r="N41">
-        <v>0.4964168598468484</v>
+        <v>0.5030260459342547</v>
       </c>
       <c r="O41">
-        <v>3.251396220200442</v>
+        <v>3.294684602206291</v>
       </c>
       <c r="P41">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="Q41">
         <v>138</v>
       </c>
       <c r="R41">
-        <v>0.05816368923971749</v>
+        <v>0.05712505193186539</v>
       </c>
       <c r="S41">
-        <v>0.4928571428571429</v>
+        <v>0.5018181818181818</v>
       </c>
       <c r="T41">
-        <v>3.250156555772994</v>
+        <v>3.309250311332503</v>
       </c>
       <c r="U41">
-        <v>0.4440167919024481</v>
+        <v>0.4524487652525271</v>
       </c>
       <c r="V41">
-        <v>0.5418342106950671</v>
+        <v>0.5511521711478127</v>
       </c>
       <c r="W41">
-        <v>2.928077857833404</v>
+        <v>2.983682679350227</v>
       </c>
       <c r="X41">
-        <v>3.573136836008292</v>
+        <v>3.634584317678863</v>
       </c>
       <c r="Y41">
-        <v>2.185775836843588E-44</v>
+        <v>1.414837171411202E-45</v>
       </c>
       <c r="Z41">
-        <v>6.557327510530763E-44</v>
+        <v>4.244511514233605E-45</v>
       </c>
     </row>
     <row r="42" spans="1:26">
@@ -4506,49 +4559,49 @@
         <v>126</v>
       </c>
       <c r="F42">
-        <v>4534</v>
+        <v>4539</v>
       </c>
       <c r="G42">
         <v>592</v>
       </c>
       <c r="H42">
-        <v>0.9418363107602825</v>
+        <v>0.9428749480681347</v>
       </c>
       <c r="I42">
-        <v>0.1305690339655933</v>
+        <v>0.1304252037893809</v>
       </c>
       <c r="J42">
-        <v>0.8610401774114604</v>
+        <v>0.8600916863590133</v>
       </c>
       <c r="K42">
-        <v>72423354.10032167</v>
+        <v>72484121.01052865</v>
       </c>
       <c r="L42">
         <v>9467672.729389539</v>
       </c>
       <c r="M42">
-        <v>0.9399730320698485</v>
+        <v>0.9407617176747385</v>
       </c>
       <c r="N42">
-        <v>0.1307267917511085</v>
+        <v>0.1306171972205377</v>
       </c>
       <c r="O42">
-        <v>0.8562251425336698</v>
+        <v>0.855507327988526</v>
       </c>
       <c r="P42">
-        <v>4534</v>
+        <v>4539</v>
       </c>
       <c r="Q42">
         <v>592</v>
       </c>
       <c r="R42">
-        <v>0.9418363107602825</v>
+        <v>0.9428749480681347</v>
       </c>
       <c r="S42">
-        <v>0.1305690339655933</v>
+        <v>0.1304252037893809</v>
       </c>
       <c r="T42">
-        <v>0.8610401774114604</v>
+        <v>0.8600916863590133</v>
       </c>
     </row>
     <row r="43" spans="1:26">
@@ -4630,67 +4683,67 @@
         <v>125</v>
       </c>
       <c r="F44">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="G44">
         <v>89</v>
       </c>
       <c r="H44">
-        <v>0.06314914831740756</v>
+        <v>0.06211051100955546</v>
       </c>
       <c r="I44">
-        <v>0.2927631578947368</v>
+        <v>0.2976588628762542</v>
       </c>
       <c r="J44">
-        <v>1.930632660418169</v>
+        <v>1.962917487515463</v>
       </c>
       <c r="K44">
-        <v>5053797.213849885</v>
+        <v>4982375.179952879</v>
       </c>
       <c r="L44">
-        <v>1489429.7101446</v>
+        <v>1489429.710144599</v>
       </c>
       <c r="M44">
-        <v>0.06559255849968333</v>
+        <v>0.06466558146868627</v>
       </c>
       <c r="N44">
-        <v>0.2947149731419438</v>
+        <v>0.298939693690166</v>
       </c>
       <c r="O44">
-        <v>1.930303394622455</v>
+        <v>1.957974172013317</v>
       </c>
       <c r="P44">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="Q44">
         <v>89</v>
       </c>
       <c r="R44">
-        <v>0.06314914831740756</v>
+        <v>0.06211051100955546</v>
       </c>
       <c r="S44">
-        <v>0.2927631578947368</v>
+        <v>0.2976588628762542</v>
       </c>
       <c r="T44">
-        <v>1.930632660418169</v>
+        <v>1.962917487515463</v>
       </c>
       <c r="U44">
-        <v>0.2518148754308999</v>
+        <v>0.2561372296192362</v>
       </c>
       <c r="V44">
-        <v>0.3373676395605241</v>
+        <v>0.3428094830771111</v>
       </c>
       <c r="W44">
-        <v>1.660598370307331</v>
+        <v>1.689102223817813</v>
       </c>
       <c r="X44">
-        <v>2.224777831293648</v>
+        <v>2.260664180182483</v>
       </c>
       <c r="Y44">
-        <v>6.342781016604726E-11</v>
+        <v>2.34460036867837E-11</v>
       </c>
       <c r="Z44">
-        <v>9.514171524907089E-11</v>
+        <v>3.516900553017555E-11</v>
       </c>
     </row>
     <row r="45" spans="1:26">
@@ -4710,49 +4763,49 @@
         <v>126</v>
       </c>
       <c r="F45">
-        <v>4510</v>
+        <v>4515</v>
       </c>
       <c r="G45">
         <v>641</v>
       </c>
       <c r="H45">
-        <v>0.9368508516825924</v>
+        <v>0.9378894889904446</v>
       </c>
       <c r="I45">
-        <v>0.1421286031042129</v>
+        <v>0.1419712070874861</v>
       </c>
       <c r="J45">
-        <v>0.9372699936214803</v>
+        <v>0.9362320423550113</v>
       </c>
       <c r="K45">
-        <v>71994534.63120668</v>
+        <v>72065956.66510367</v>
       </c>
       <c r="L45">
-        <v>10274159.9481478</v>
+        <v>10274159.94814779</v>
       </c>
       <c r="M45">
-        <v>0.9344074415003168</v>
+        <v>0.9353344185313138</v>
       </c>
       <c r="N45">
-        <v>0.1427074985730149</v>
+        <v>0.1425660661925664</v>
       </c>
       <c r="O45">
-        <v>0.9346955331003679</v>
+        <v>0.9337691892462412</v>
       </c>
       <c r="P45">
-        <v>4510</v>
+        <v>4515</v>
       </c>
       <c r="Q45">
         <v>641</v>
       </c>
       <c r="R45">
-        <v>0.9368508516825924</v>
+        <v>0.9378894889904446</v>
       </c>
       <c r="S45">
-        <v>0.1421286031042129</v>
+        <v>0.1419712070874861</v>
       </c>
       <c r="T45">
-        <v>0.9372699936214803</v>
+        <v>0.9362320423550113</v>
       </c>
     </row>
     <row r="46" spans="1:26">
@@ -4834,67 +4887,67 @@
         <v>125</v>
       </c>
       <c r="F47">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G47">
         <v>83</v>
       </c>
       <c r="H47">
-        <v>0.0666805151641047</v>
+        <v>0.06647278770253427</v>
       </c>
       <c r="I47">
-        <v>0.2585669781931464</v>
+        <v>0.259375</v>
       </c>
       <c r="J47">
-        <v>1.705125250714804</v>
+        <v>1.710453767123288</v>
       </c>
       <c r="K47">
-        <v>5008419.879757558</v>
+        <v>4983469.560449703</v>
       </c>
       <c r="L47">
-        <v>1243079.988899842</v>
+        <v>1243079.988899841</v>
       </c>
       <c r="M47">
-        <v>0.06500361214606751</v>
+        <v>0.06467978528686918</v>
       </c>
       <c r="N47">
-        <v>0.2481980382523391</v>
+        <v>0.249440670565201</v>
       </c>
       <c r="O47">
-        <v>1.625630047464117</v>
+        <v>1.633768953153953</v>
       </c>
       <c r="P47">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q47">
         <v>83</v>
       </c>
       <c r="R47">
-        <v>0.0666805151641047</v>
+        <v>0.06647278770253427</v>
       </c>
       <c r="S47">
-        <v>0.2585669781931464</v>
+        <v>0.259375</v>
       </c>
       <c r="T47">
-        <v>1.705125250714804</v>
+        <v>1.710453767123288</v>
       </c>
       <c r="U47">
-        <v>0.2205050600669506</v>
+        <v>0.2212100362540926</v>
       </c>
       <c r="V47">
-        <v>0.3006647093905795</v>
+        <v>0.3015747341850729</v>
       </c>
       <c r="W47">
-        <v>1.454125149537398</v>
+        <v>1.458774129489318</v>
       </c>
       <c r="X47">
-        <v>1.982739604118151</v>
+        <v>1.988740781324576</v>
       </c>
       <c r="Y47">
-        <v>1.760180906908011E-07</v>
+        <v>1.518689815764981E-07</v>
       </c>
       <c r="Z47">
-        <v>1.760180906908011E-07</v>
+        <v>1.518689815764981E-07</v>
       </c>
     </row>
     <row r="48" spans="1:26">
@@ -4914,49 +4967,49 @@
         <v>126</v>
       </c>
       <c r="F48">
-        <v>4493</v>
+        <v>4494</v>
       </c>
       <c r="G48">
         <v>647</v>
       </c>
       <c r="H48">
-        <v>0.9333194848358953</v>
+        <v>0.9335272122974657</v>
       </c>
       <c r="I48">
-        <v>0.1440017805475184</v>
+        <v>0.1439697374276813</v>
       </c>
       <c r="J48">
-        <v>0.9496227007613059</v>
+        <v>0.9494113917491206</v>
       </c>
       <c r="K48">
-        <v>72039911.96529901</v>
+        <v>72064862.28460686</v>
       </c>
       <c r="L48">
         <v>10520509.66939255</v>
       </c>
       <c r="M48">
-        <v>0.9349963878539328</v>
+        <v>0.935320214713131</v>
       </c>
       <c r="N48">
-        <v>0.1460372366148946</v>
+        <v>0.145986675556858</v>
       </c>
       <c r="O48">
-        <v>0.9565044170431204</v>
+        <v>0.9561732557827223</v>
       </c>
       <c r="P48">
-        <v>4493</v>
+        <v>4494</v>
       </c>
       <c r="Q48">
         <v>647</v>
       </c>
       <c r="R48">
-        <v>0.9333194848358953</v>
+        <v>0.9335272122974657</v>
       </c>
       <c r="S48">
-        <v>0.1440017805475184</v>
+        <v>0.1439697374276813</v>
       </c>
       <c r="T48">
-        <v>0.9496227007613059</v>
+        <v>0.9494113917491206</v>
       </c>
     </row>
     <row r="49" spans="1:20">
@@ -5128,67 +5181,67 @@
         <v>125</v>
       </c>
       <c r="F2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G2">
         <v>64</v>
       </c>
       <c r="H2">
-        <v>0.06233207952713595</v>
+        <v>0.06072004298764105</v>
       </c>
       <c r="I2">
-        <v>0.5517241379310345</v>
+        <v>0.5663716814159292</v>
       </c>
       <c r="J2">
-        <v>3.159257294429708</v>
+        <v>3.243131381892444</v>
       </c>
       <c r="K2">
-        <v>1829410.634804715</v>
+        <v>1783794.714852137</v>
       </c>
       <c r="L2">
         <v>981743.4282125103</v>
       </c>
       <c r="M2">
-        <v>0.0618900180286246</v>
+        <v>0.06034680511920654</v>
       </c>
       <c r="N2">
-        <v>0.5366446491207312</v>
+        <v>0.5503679431485978</v>
       </c>
       <c r="O2">
-        <v>3.107239254533693</v>
+        <v>3.186698833558214</v>
       </c>
       <c r="P2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="Q2">
         <v>64</v>
       </c>
       <c r="R2">
-        <v>0.06233207952713595</v>
+        <v>0.06072004298764105</v>
       </c>
       <c r="S2">
-        <v>0.5517241379310345</v>
+        <v>0.5663716814159292</v>
       </c>
       <c r="T2">
-        <v>3.159257294429708</v>
+        <v>3.243131381892444</v>
       </c>
       <c r="U2">
-        <v>0.4754557826608937</v>
+        <v>0.4890229220110073</v>
       </c>
       <c r="V2">
-        <v>0.6256346942521792</v>
+        <v>0.6406165019285297</v>
       </c>
       <c r="W2">
-        <v>2.722532958559763</v>
+        <v>2.800220485730722</v>
       </c>
       <c r="X2">
-        <v>3.582480510779402</v>
+        <v>3.668268646427673</v>
       </c>
       <c r="Y2">
-        <v>1.174749824247042E-21</v>
+        <v>1.64847748376523E-22</v>
       </c>
       <c r="Z2">
-        <v>3.524249472741127E-21</v>
+        <v>4.945432451295689E-22</v>
       </c>
     </row>
     <row r="3" spans="1:26">
@@ -5208,49 +5261,49 @@
         <v>126</v>
       </c>
       <c r="F3">
-        <v>1745</v>
+        <v>1748</v>
       </c>
       <c r="G3">
         <v>261</v>
       </c>
       <c r="H3">
-        <v>0.9376679204728641</v>
+        <v>0.939279957012359</v>
       </c>
       <c r="I3">
-        <v>0.1495702005730659</v>
+        <v>0.1493135011441648</v>
       </c>
       <c r="J3">
-        <v>0.8564619792814636</v>
+        <v>0.8549920788593557</v>
       </c>
       <c r="K3">
-        <v>27729647.401963</v>
+        <v>27775263.32191557</v>
       </c>
       <c r="L3">
         <v>4123338.295164815</v>
       </c>
       <c r="M3">
-        <v>0.9381099819713754</v>
+        <v>0.9396531948807934</v>
       </c>
       <c r="N3">
-        <v>0.1486978263875408</v>
+        <v>0.148453616708338</v>
       </c>
       <c r="O3">
-        <v>0.8609789065673803</v>
+        <v>0.8595649021553378</v>
       </c>
       <c r="P3">
-        <v>1745</v>
+        <v>1748</v>
       </c>
       <c r="Q3">
         <v>261</v>
       </c>
       <c r="R3">
-        <v>0.9376679204728641</v>
+        <v>0.939279957012359</v>
       </c>
       <c r="S3">
-        <v>0.1495702005730659</v>
+        <v>0.1493135011441648</v>
       </c>
       <c r="T3">
-        <v>0.8564619792814636</v>
+        <v>0.8549920788593557</v>
       </c>
     </row>
     <row r="4" spans="1:26">
@@ -5332,67 +5385,67 @@
         <v>125</v>
       </c>
       <c r="F5">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G5">
         <v>56</v>
       </c>
       <c r="H5">
-        <v>0.07039226222461042</v>
+        <v>0.0693175711982805</v>
       </c>
       <c r="I5">
-        <v>0.4274809160305343</v>
+        <v>0.4341085271317829</v>
       </c>
       <c r="J5">
-        <v>2.447821491485614</v>
+        <v>2.48577221228384</v>
       </c>
       <c r="K5">
-        <v>2162980.245655169</v>
+        <v>2123415.619562232</v>
       </c>
       <c r="L5">
         <v>953713.9351679728</v>
       </c>
       <c r="M5">
-        <v>0.07317487055794189</v>
+        <v>0.07183637641365205</v>
       </c>
       <c r="N5">
-        <v>0.440925864710841</v>
+        <v>0.4491414334441942</v>
       </c>
       <c r="O5">
-        <v>2.553015589391461</v>
+        <v>2.600584754030335</v>
       </c>
       <c r="P5">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="Q5">
         <v>56</v>
       </c>
       <c r="R5">
-        <v>0.07039226222461042</v>
+        <v>0.0693175711982805</v>
       </c>
       <c r="S5">
-        <v>0.4274809160305343</v>
+        <v>0.4341085271317829</v>
       </c>
       <c r="T5">
-        <v>2.447821491485614</v>
+        <v>2.48577221228384</v>
       </c>
       <c r="U5">
-        <v>0.3585600750598154</v>
+        <v>0.3644111607908513</v>
       </c>
       <c r="V5">
-        <v>0.4993366171104446</v>
+        <v>0.506513026952809</v>
       </c>
       <c r="W5">
-        <v>2.053170152880973</v>
+        <v>2.086674369943921</v>
       </c>
       <c r="X5">
-        <v>2.859278290592423</v>
+        <v>2.900371517412854</v>
       </c>
       <c r="Y5">
-        <v>1.445072713872563E-12</v>
+        <v>6.544019142128437E-13</v>
       </c>
       <c r="Z5">
-        <v>2.167609070808844E-12</v>
+        <v>9.816028713192654E-13</v>
       </c>
     </row>
     <row r="6" spans="1:26">
@@ -5412,49 +5465,49 @@
         <v>126</v>
       </c>
       <c r="F6">
-        <v>1730</v>
+        <v>1732</v>
       </c>
       <c r="G6">
         <v>269</v>
       </c>
       <c r="H6">
-        <v>0.9296077377753896</v>
+        <v>0.9306824288017195</v>
       </c>
       <c r="I6">
-        <v>0.1554913294797688</v>
+        <v>0.1553117782909931</v>
       </c>
       <c r="J6">
-        <v>0.890367274344153</v>
+        <v>0.8893391366139635</v>
       </c>
       <c r="K6">
-        <v>27396077.79111255</v>
+        <v>27435642.41720548</v>
       </c>
       <c r="L6">
         <v>4151367.788209352</v>
       </c>
       <c r="M6">
-        <v>0.9268251294420582</v>
+        <v>0.928163623586348</v>
       </c>
       <c r="N6">
-        <v>0.1515314644622626</v>
+        <v>0.1513129426707333</v>
       </c>
       <c r="O6">
-        <v>0.8773860234059498</v>
+        <v>0.8761207550580341</v>
       </c>
       <c r="P6">
-        <v>1730</v>
+        <v>1732</v>
       </c>
       <c r="Q6">
         <v>269</v>
       </c>
       <c r="R6">
-        <v>0.9296077377753896</v>
+        <v>0.9306824288017195</v>
       </c>
       <c r="S6">
-        <v>0.1554913294797688</v>
+        <v>0.1553117782909931</v>
       </c>
       <c r="T6">
-        <v>0.890367274344153</v>
+        <v>0.8893391366139635</v>
       </c>
     </row>
     <row r="7" spans="1:26">
@@ -5740,67 +5793,67 @@
         <v>125</v>
       </c>
       <c r="F11">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G11">
         <v>53</v>
       </c>
       <c r="H11">
-        <v>0.05747126436781609</v>
+        <v>0.05582922824302135</v>
       </c>
       <c r="I11">
-        <v>0.5047619047619047</v>
+        <v>0.5196078431372549</v>
       </c>
       <c r="J11">
-        <v>3.519847328244275</v>
+        <v>3.623372249663224</v>
       </c>
       <c r="K11">
-        <v>1697830.033532121</v>
+        <v>1662672.556848676</v>
       </c>
       <c r="L11">
         <v>900829.766690349</v>
       </c>
       <c r="M11">
-        <v>0.0576025578974004</v>
+        <v>0.05640976442208913</v>
       </c>
       <c r="N11">
-        <v>0.5305771183799161</v>
+        <v>0.5417962562621015</v>
       </c>
       <c r="O11">
-        <v>3.621483864247343</v>
+        <v>3.698060718777296</v>
       </c>
       <c r="P11">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="Q11">
         <v>53</v>
       </c>
       <c r="R11">
-        <v>0.05747126436781609</v>
+        <v>0.05582922824302135</v>
       </c>
       <c r="S11">
-        <v>0.5047619047619047</v>
+        <v>0.5196078431372549</v>
       </c>
       <c r="T11">
-        <v>3.519847328244275</v>
+        <v>3.623372249663224</v>
       </c>
       <c r="U11">
-        <v>0.4253996292300799</v>
+        <v>0.4387879976219711</v>
       </c>
       <c r="V11">
-        <v>0.5838849439490732</v>
+        <v>0.5994143732176748</v>
       </c>
       <c r="W11">
-        <v>2.966431765661664</v>
+        <v>3.059792639905883</v>
       </c>
       <c r="X11">
-        <v>4.071594628225026</v>
+        <v>4.179885724689663</v>
       </c>
       <c r="Y11">
-        <v>7.198286085767341E-20</v>
+        <v>1.239322992328452E-20</v>
       </c>
       <c r="Z11">
-        <v>2.159485825730202E-19</v>
+        <v>3.717968976985356E-20</v>
       </c>
     </row>
     <row r="12" spans="1:26">
@@ -5820,49 +5873,49 @@
         <v>126</v>
       </c>
       <c r="F12">
-        <v>1722</v>
+        <v>1725</v>
       </c>
       <c r="G12">
         <v>209</v>
       </c>
       <c r="H12">
-        <v>0.9425287356321839</v>
+        <v>0.9441707717569786</v>
       </c>
       <c r="I12">
-        <v>0.1213704994192799</v>
+        <v>0.1211594202898551</v>
       </c>
       <c r="J12">
-        <v>0.846350772668032</v>
+        <v>0.8448788582807832</v>
       </c>
       <c r="K12">
-        <v>27777076.90647278</v>
+        <v>27812234.38315623</v>
       </c>
       <c r="L12">
         <v>3417486.088071632</v>
       </c>
       <c r="M12">
-        <v>0.9423974421025997</v>
+        <v>0.9435902355779109</v>
       </c>
       <c r="N12">
-        <v>0.1230326034513469</v>
+        <v>0.1228770777993064</v>
       </c>
       <c r="O12">
-        <v>0.8397659317384176</v>
+        <v>0.8387043826820597</v>
       </c>
       <c r="P12">
-        <v>1722</v>
+        <v>1725</v>
       </c>
       <c r="Q12">
         <v>209</v>
       </c>
       <c r="R12">
-        <v>0.9425287356321839</v>
+        <v>0.9441707717569786</v>
       </c>
       <c r="S12">
-        <v>0.1213704994192799</v>
+        <v>0.1211594202898551</v>
       </c>
       <c r="T12">
-        <v>0.846350772668032</v>
+        <v>0.8448788582807832</v>
       </c>
     </row>
     <row r="13" spans="1:26">
@@ -5944,67 +5997,67 @@
         <v>125</v>
       </c>
       <c r="F14">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G14">
         <v>35</v>
       </c>
       <c r="H14">
-        <v>0.0541871921182266</v>
+        <v>0.05363984674329502</v>
       </c>
       <c r="I14">
-        <v>0.3535353535353535</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="J14">
-        <v>2.46530187369882</v>
+        <v>2.490458015267176</v>
       </c>
       <c r="K14">
-        <v>1607391.567975017</v>
+        <v>1579218.907215925</v>
       </c>
       <c r="L14">
         <v>520796.2894998041</v>
       </c>
       <c r="M14">
-        <v>0.05453423724956295</v>
+        <v>0.05357841876923879</v>
       </c>
       <c r="N14">
-        <v>0.3240008843370384</v>
+        <v>0.3297809360818373</v>
       </c>
       <c r="O14">
-        <v>2.211486198672207</v>
+        <v>2.250938265870694</v>
       </c>
       <c r="P14">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q14">
         <v>35</v>
       </c>
       <c r="R14">
-        <v>0.0541871921182266</v>
+        <v>0.05363984674329502</v>
       </c>
       <c r="S14">
-        <v>0.3535353535353535</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="T14">
-        <v>2.46530187369882</v>
+        <v>2.490458015267176</v>
       </c>
       <c r="U14">
-        <v>0.2793613697958147</v>
+        <v>0.2823493088476176</v>
       </c>
       <c r="V14">
-        <v>0.4355017633716602</v>
+        <v>0.4396123723108459</v>
       </c>
       <c r="W14">
-        <v>1.948065735179212</v>
+        <v>1.96890147810915</v>
       </c>
       <c r="X14">
-        <v>3.036876800305432</v>
+        <v>3.065541237450059</v>
       </c>
       <c r="Y14">
-        <v>5.465032169638598E-08</v>
+        <v>4.043616246082304E-08</v>
       </c>
       <c r="Z14">
-        <v>8.197548254457897E-08</v>
+        <v>6.065424369123455E-08</v>
       </c>
     </row>
     <row r="15" spans="1:26">
@@ -6024,49 +6077,49 @@
         <v>126</v>
       </c>
       <c r="F15">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="G15">
         <v>227</v>
       </c>
       <c r="H15">
-        <v>0.9458128078817734</v>
+        <v>0.946360153256705</v>
       </c>
       <c r="I15">
-        <v>0.1313657407407407</v>
+        <v>0.1312897628687102</v>
       </c>
       <c r="J15">
-        <v>0.916050413486005</v>
+        <v>0.9155205983249375</v>
       </c>
       <c r="K15">
-        <v>27867515.37202989</v>
+        <v>27895688.03278898</v>
       </c>
       <c r="L15">
         <v>3797519.565262177</v>
       </c>
       <c r="M15">
-        <v>0.9454657627504371</v>
+        <v>0.9464215812307613</v>
       </c>
       <c r="N15">
-        <v>0.136270475303072</v>
+        <v>0.1361328518156111</v>
       </c>
       <c r="O15">
-        <v>0.9301217681423325</v>
+        <v>0.9291824113138607</v>
       </c>
       <c r="P15">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="Q15">
         <v>227</v>
       </c>
       <c r="R15">
-        <v>0.9458128078817734</v>
+        <v>0.946360153256705</v>
       </c>
       <c r="S15">
-        <v>0.1313657407407407</v>
+        <v>0.1312897628687102</v>
       </c>
       <c r="T15">
-        <v>0.916050413486005</v>
+        <v>0.9155205983249375</v>
       </c>
     </row>
     <row r="16" spans="1:26">
@@ -6148,67 +6201,67 @@
         <v>125</v>
       </c>
       <c r="F17">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G17">
         <v>35</v>
       </c>
       <c r="H17">
-        <v>0.06513409961685823</v>
+        <v>0.06458675424192666</v>
       </c>
       <c r="I17">
-        <v>0.2941176470588235</v>
+        <v>0.2966101694915254</v>
       </c>
       <c r="J17">
-        <v>2.050965424337674</v>
+        <v>2.06834648725579</v>
       </c>
       <c r="K17">
-        <v>1756867.548444361</v>
+        <v>1753447.368426784</v>
       </c>
       <c r="L17">
         <v>529791.4647318212</v>
       </c>
       <c r="M17">
-        <v>0.05960553334469895</v>
+        <v>0.05948949633652322</v>
       </c>
       <c r="N17">
-        <v>0.3015545851483974</v>
+        <v>0.302142781284138</v>
       </c>
       <c r="O17">
-        <v>2.058277725280173</v>
+        <v>2.062292490977385</v>
       </c>
       <c r="P17">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q17">
         <v>35</v>
       </c>
       <c r="R17">
-        <v>0.06513409961685823</v>
+        <v>0.06458675424192666</v>
       </c>
       <c r="S17">
-        <v>0.2941176470588235</v>
+        <v>0.2966101694915254</v>
       </c>
       <c r="T17">
-        <v>2.050965424337674</v>
+        <v>2.06834648725579</v>
       </c>
       <c r="U17">
-        <v>0.2306046529193002</v>
+        <v>0.2326332081966284</v>
       </c>
       <c r="V17">
-        <v>0.3667842694802642</v>
+        <v>0.3697048565977652</v>
       </c>
       <c r="W17">
-        <v>1.608071377418174</v>
+        <v>1.62221706631771</v>
       </c>
       <c r="X17">
-        <v>2.557690306642911</v>
+        <v>2.578056385511897</v>
       </c>
       <c r="Y17">
-        <v>8.312906356745645E-06</v>
+        <v>6.722494191573021E-06</v>
       </c>
       <c r="Z17">
-        <v>8.312906356745645E-06</v>
+        <v>6.722494191573021E-06</v>
       </c>
     </row>
     <row r="18" spans="1:26">
@@ -6228,49 +6281,49 @@
         <v>126</v>
       </c>
       <c r="F18">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="G18">
         <v>227</v>
       </c>
       <c r="H18">
-        <v>0.9348659003831418</v>
+        <v>0.9354132457580734</v>
       </c>
       <c r="I18">
-        <v>0.132903981264637</v>
+        <v>0.1328262141603277</v>
       </c>
       <c r="J18">
-        <v>0.9267769991240146</v>
+        <v>0.9262347071409108</v>
       </c>
       <c r="K18">
-        <v>27718039.39156054</v>
+        <v>27721459.57157812</v>
       </c>
       <c r="L18">
         <v>3788524.39003016</v>
       </c>
       <c r="M18">
-        <v>0.940394466655301</v>
+        <v>0.9405105036634768</v>
       </c>
       <c r="N18">
-        <v>0.1366808213420633</v>
+        <v>0.1366639581241389</v>
       </c>
       <c r="O18">
-        <v>0.9329226080343781</v>
+        <v>0.9328075071951274</v>
       </c>
       <c r="P18">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="Q18">
         <v>227</v>
       </c>
       <c r="R18">
-        <v>0.9348659003831418</v>
+        <v>0.9354132457580734</v>
       </c>
       <c r="S18">
-        <v>0.132903981264637</v>
+        <v>0.1328262141603277</v>
       </c>
       <c r="T18">
-        <v>0.9267769991240146</v>
+        <v>0.9262347071409108</v>
       </c>
     </row>
     <row r="19" spans="1:26">
@@ -6556,67 +6609,67 @@
         <v>125</v>
       </c>
       <c r="F23">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G23">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H23">
-        <v>0.06172839506172839</v>
+        <v>0.06011808910359635</v>
       </c>
       <c r="I23">
-        <v>0.4173913043478261</v>
+        <v>0.4107142857142857</v>
       </c>
       <c r="J23">
-        <v>2.63593220338983</v>
+        <v>2.593765133171912</v>
       </c>
       <c r="K23">
-        <v>1828866.17766177</v>
+        <v>1810062.397266268</v>
       </c>
       <c r="L23">
-        <v>855563.5375871824</v>
+        <v>841658.7484874979</v>
       </c>
       <c r="M23">
-        <v>0.06195562841140193</v>
+        <v>0.06131862169918702</v>
       </c>
       <c r="N23">
-        <v>0.467810902753438</v>
+        <v>0.4649888035675746</v>
       </c>
       <c r="O23">
-        <v>2.841104355581236</v>
+        <v>2.823965211876703</v>
       </c>
       <c r="P23">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="Q23">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="R23">
-        <v>0.06172839506172839</v>
+        <v>0.06011808910359635</v>
       </c>
       <c r="S23">
-        <v>0.4173913043478261</v>
+        <v>0.4107142857142857</v>
       </c>
       <c r="T23">
-        <v>2.63593220338983</v>
+        <v>2.593765133171912</v>
       </c>
       <c r="U23">
-        <v>0.3445026247856228</v>
+        <v>0.3372350926347694</v>
       </c>
       <c r="V23">
-        <v>0.4940776200997006</v>
+        <v>0.4884054178606635</v>
       </c>
       <c r="W23">
-        <v>2.175621660934289</v>
+        <v>2.129725347723984</v>
       </c>
       <c r="X23">
-        <v>3.120225783883872</v>
+        <v>3.084404384659038</v>
       </c>
       <c r="Y23">
-        <v>4.635825059896115E-12</v>
+        <v>2.759789406390189E-11</v>
       </c>
       <c r="Z23">
-        <v>6.953737589844172E-12</v>
+        <v>4.139684109585284E-11</v>
       </c>
     </row>
     <row r="24" spans="1:26">
@@ -6636,49 +6689,49 @@
         <v>126</v>
       </c>
       <c r="F24">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="G24">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H24">
-        <v>0.9382716049382716</v>
+        <v>0.9398819108964036</v>
       </c>
       <c r="I24">
-        <v>0.1413043478260869</v>
+        <v>0.1422044545973729</v>
       </c>
       <c r="J24">
-        <v>0.8923728813559321</v>
+        <v>0.8980572844573077</v>
       </c>
       <c r="K24">
-        <v>27690101.2600924</v>
+        <v>27708905.0404879</v>
       </c>
       <c r="L24">
-        <v>4004974.153778258</v>
+        <v>4018878.942877942</v>
       </c>
       <c r="M24">
-        <v>0.9380443715885981</v>
+        <v>0.9386813783008131</v>
       </c>
       <c r="N24">
-        <v>0.1446355907535202</v>
+        <v>0.1450392549617391</v>
       </c>
       <c r="O24">
-        <v>0.8783993798418829</v>
+        <v>0.8808509091530059</v>
       </c>
       <c r="P24">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="Q24">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="R24">
-        <v>0.9382716049382716</v>
+        <v>0.9398819108964036</v>
       </c>
       <c r="S24">
-        <v>0.1413043478260869</v>
+        <v>0.1422044545973729</v>
       </c>
       <c r="T24">
-        <v>0.8923728813559321</v>
+        <v>0.8980572844573077</v>
       </c>
     </row>
     <row r="25" spans="1:26">
@@ -6760,67 +6813,67 @@
         <v>125</v>
       </c>
       <c r="F26">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G26">
         <v>34</v>
       </c>
       <c r="H26">
-        <v>0.06870638754696726</v>
+        <v>0.06816961889425657</v>
       </c>
       <c r="I26">
-        <v>0.265625</v>
+        <v>0.2677165354330709</v>
       </c>
       <c r="J26">
-        <v>1.677489406779661</v>
+        <v>1.6906979847858</v>
       </c>
       <c r="K26">
-        <v>1979866.492689391</v>
+        <v>1954610.325847302</v>
       </c>
       <c r="L26">
         <v>543130.7300911016</v>
       </c>
       <c r="M26">
-        <v>0.06707099416211899</v>
+        <v>0.06621540302752575</v>
       </c>
       <c r="N26">
-        <v>0.274326946840405</v>
+        <v>0.2778716161011073</v>
       </c>
       <c r="O26">
-        <v>1.666039587650139</v>
+        <v>1.687567036489833</v>
       </c>
       <c r="P26">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q26">
         <v>34</v>
       </c>
       <c r="R26">
-        <v>0.06870638754696726</v>
+        <v>0.06816961889425657</v>
       </c>
       <c r="S26">
-        <v>0.265625</v>
+        <v>0.2677165354330709</v>
       </c>
       <c r="T26">
-        <v>1.677489406779661</v>
+        <v>1.6906979847858</v>
       </c>
       <c r="U26">
-        <v>0.2067476509954731</v>
+        <v>0.2084307288088889</v>
       </c>
       <c r="V26">
-        <v>0.3342052541804854</v>
+        <v>0.3366927992315229</v>
       </c>
       <c r="W26">
-        <v>1.30566397899853</v>
+        <v>1.31629304329139</v>
       </c>
       <c r="X26">
-        <v>2.110591147587269</v>
+        <v>2.126300627011279</v>
       </c>
       <c r="Y26">
-        <v>0.0008732926085829959</v>
+        <v>0.0007479410761105923</v>
       </c>
       <c r="Z26">
-        <v>0.0008732926085829959</v>
+        <v>0.0007479410761105923</v>
       </c>
     </row>
     <row r="27" spans="1:26">
@@ -6840,49 +6893,49 @@
         <v>126</v>
       </c>
       <c r="F27">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="G27">
         <v>261</v>
       </c>
       <c r="H27">
-        <v>0.9312936124530328</v>
+        <v>0.9318303811057435</v>
       </c>
       <c r="I27">
-        <v>0.1504322766570605</v>
+        <v>0.1503456221198157</v>
       </c>
       <c r="J27">
-        <v>0.9500180725834025</v>
+        <v>0.9494708271498867</v>
       </c>
       <c r="K27">
-        <v>27539100.94506478</v>
+        <v>27564357.11190687</v>
       </c>
       <c r="L27">
         <v>4317406.961274339</v>
       </c>
       <c r="M27">
-        <v>0.9329290058378811</v>
+        <v>0.9337845969724743</v>
       </c>
       <c r="N27">
-        <v>0.1567737076779208</v>
+        <v>0.1566300619218638</v>
       </c>
       <c r="O27">
-        <v>0.9521164665097941</v>
+        <v>0.9512440785838343</v>
       </c>
       <c r="P27">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="Q27">
         <v>261</v>
       </c>
       <c r="R27">
-        <v>0.9312936124530328</v>
+        <v>0.9318303811057435</v>
       </c>
       <c r="S27">
-        <v>0.1504322766570605</v>
+        <v>0.1503456221198157</v>
       </c>
       <c r="T27">
-        <v>0.9500180725834025</v>
+        <v>0.9494708271498867</v>
       </c>
     </row>
     <row r="28" spans="1:26">
@@ -6964,67 +7017,67 @@
         <v>125</v>
       </c>
       <c r="F29">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G29">
         <v>45</v>
       </c>
       <c r="H29">
-        <v>0.06190777005685408</v>
+        <v>0.06001263423878711</v>
       </c>
       <c r="I29">
-        <v>0.4591836734693878</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="J29">
-        <v>2.89596715180096</v>
+        <v>2.987418746068358</v>
       </c>
       <c r="K29">
-        <v>1519524.298934708</v>
+        <v>1473908.378982131</v>
       </c>
       <c r="L29">
         <v>628038.9749923479</v>
       </c>
       <c r="M29">
-        <v>0.06017714906926734</v>
+        <v>0.05837063895498851</v>
       </c>
       <c r="N29">
-        <v>0.4133128870875226</v>
+        <v>0.42610448786923</v>
       </c>
       <c r="O29">
-        <v>2.766762093323673</v>
+        <v>2.852390481069209</v>
       </c>
       <c r="P29">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q29">
         <v>45</v>
       </c>
       <c r="R29">
-        <v>0.06190777005685408</v>
+        <v>0.06001263423878711</v>
       </c>
       <c r="S29">
-        <v>0.4591836734693878</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="T29">
-        <v>2.89596715180096</v>
+        <v>2.987418746068358</v>
       </c>
       <c r="U29">
-        <v>0.3785923239976577</v>
+        <v>0.3913222934134113</v>
       </c>
       <c r="V29">
-        <v>0.5419681563333318</v>
+        <v>0.5575035375145019</v>
       </c>
       <c r="W29">
-        <v>2.387695812303952</v>
+        <v>2.467980838539563</v>
       </c>
       <c r="X29">
-        <v>3.418070085560415</v>
+        <v>3.516048206714966</v>
       </c>
       <c r="Y29">
-        <v>2.758586288369854E-13</v>
+        <v>6.559781053565001E-14</v>
       </c>
       <c r="Z29">
-        <v>8.275758865109563E-13</v>
+        <v>1.9679343160695E-13</v>
       </c>
     </row>
     <row r="30" spans="1:26">
@@ -7044,49 +7097,49 @@
         <v>126</v>
       </c>
       <c r="F30">
-        <v>1485</v>
+        <v>1488</v>
       </c>
       <c r="G30">
         <v>206</v>
       </c>
       <c r="H30">
-        <v>0.9380922299431459</v>
+        <v>0.9399873657612129</v>
       </c>
       <c r="I30">
-        <v>0.1387205387205387</v>
+        <v>0.1384408602150538</v>
       </c>
       <c r="J30">
-        <v>0.8748789354367043</v>
+        <v>0.8731150666152593</v>
       </c>
       <c r="K30">
-        <v>23731327.93378986</v>
+        <v>23776943.85374243</v>
       </c>
       <c r="L30">
         <v>3144060.788450117</v>
       </c>
       <c r="M30">
-        <v>0.9398228509307328</v>
+        <v>0.9416293610450115</v>
       </c>
       <c r="N30">
-        <v>0.1324856660875452</v>
+        <v>0.1322314931553009</v>
       </c>
       <c r="O30">
-        <v>0.886873674379614</v>
+        <v>0.8851722127120675</v>
       </c>
       <c r="P30">
-        <v>1485</v>
+        <v>1488</v>
       </c>
       <c r="Q30">
         <v>206</v>
       </c>
       <c r="R30">
-        <v>0.9380922299431459</v>
+        <v>0.9399873657612129</v>
       </c>
       <c r="S30">
-        <v>0.1387205387205387</v>
+        <v>0.1384408602150538</v>
       </c>
       <c r="T30">
-        <v>0.8748789354367043</v>
+        <v>0.8731150666152593</v>
       </c>
     </row>
     <row r="31" spans="1:26">
@@ -7168,67 +7221,67 @@
         <v>125</v>
       </c>
       <c r="F32">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G32">
         <v>32</v>
       </c>
       <c r="H32">
-        <v>0.06948831332912192</v>
+        <v>0.06885660138976626</v>
       </c>
       <c r="I32">
-        <v>0.2909090909090909</v>
+        <v>0.2935779816513762</v>
       </c>
       <c r="J32">
-        <v>1.834697573342992</v>
+        <v>1.851529661171826</v>
       </c>
       <c r="K32">
-        <v>1803580.135146062</v>
+        <v>1779134.542403648</v>
       </c>
       <c r="L32">
         <v>553858.4072335805</v>
       </c>
       <c r="M32">
-        <v>0.07142650547091876</v>
+        <v>0.07045839585952383</v>
       </c>
       <c r="N32">
-        <v>0.3070883275107299</v>
+        <v>0.3113077701730787</v>
       </c>
       <c r="O32">
-        <v>2.05568316498908</v>
+        <v>2.083928579970944</v>
       </c>
       <c r="P32">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="Q32">
         <v>32</v>
       </c>
       <c r="R32">
-        <v>0.06948831332912192</v>
+        <v>0.06885660138976626</v>
       </c>
       <c r="S32">
-        <v>0.2909090909090909</v>
+        <v>0.2935779816513762</v>
       </c>
       <c r="T32">
-        <v>1.834697573342992</v>
+        <v>1.851529661171826</v>
       </c>
       <c r="U32">
-        <v>0.2253801625783378</v>
+        <v>0.2275279855995238</v>
       </c>
       <c r="V32">
-        <v>0.3664766477414169</v>
+        <v>0.3696271903341358</v>
       </c>
       <c r="W32">
-        <v>1.421421503432306</v>
+        <v>1.434967335474288</v>
       </c>
       <c r="X32">
-        <v>2.311284993524553</v>
+        <v>2.331154750194968</v>
       </c>
       <c r="Y32">
-        <v>0.0001975659308321416</v>
+        <v>0.0001631096746532775</v>
       </c>
       <c r="Z32">
-        <v>0.0002963488962482124</v>
+        <v>0.0002446645119799163</v>
       </c>
     </row>
     <row r="33" spans="1:26">
@@ -7248,49 +7301,49 @@
         <v>126</v>
       </c>
       <c r="F33">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="G33">
         <v>219</v>
       </c>
       <c r="H33">
-        <v>0.930511686670878</v>
+        <v>0.9311433986102338</v>
       </c>
       <c r="I33">
-        <v>0.1486761710794297</v>
+        <v>0.1485753052917232</v>
       </c>
       <c r="J33">
-        <v>0.9376668478834154</v>
+        <v>0.9370307102661267</v>
       </c>
       <c r="K33">
-        <v>23447272.0975785</v>
+        <v>23471717.69032092</v>
       </c>
       <c r="L33">
         <v>3218241.356208884</v>
       </c>
       <c r="M33">
-        <v>0.9285734945290812</v>
+        <v>0.9295416041404763</v>
       </c>
       <c r="N33">
-        <v>0.1372544039586271</v>
+        <v>0.1371114546736389</v>
       </c>
       <c r="O33">
-        <v>0.9187961321274954</v>
+        <v>0.9178392138330769</v>
       </c>
       <c r="P33">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="Q33">
         <v>219</v>
       </c>
       <c r="R33">
-        <v>0.930511686670878</v>
+        <v>0.9311433986102338</v>
       </c>
       <c r="S33">
-        <v>0.1486761710794297</v>
+        <v>0.1485753052917232</v>
       </c>
       <c r="T33">
-        <v>0.9376668478834154</v>
+        <v>0.9370307102661267</v>
       </c>
     </row>
     <row r="34" spans="1:26">
@@ -7576,67 +7629,67 @@
         <v>125</v>
       </c>
       <c r="F38">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G38">
         <v>50</v>
       </c>
       <c r="H38">
-        <v>0.06071871127633209</v>
+        <v>0.05947955390334572</v>
       </c>
       <c r="I38">
-        <v>0.5102040816326531</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="J38">
-        <v>3.812358276643991</v>
+        <v>3.891782407407408</v>
       </c>
       <c r="K38">
-        <v>1583221.53847368</v>
+        <v>1568070.548219264</v>
       </c>
       <c r="L38">
         <v>857791.2474685709</v>
       </c>
       <c r="M38">
-        <v>0.06095716312843178</v>
+        <v>0.06037382001311129</v>
       </c>
       <c r="N38">
-        <v>0.5418011482433044</v>
+        <v>0.5470361320431009</v>
       </c>
       <c r="O38">
-        <v>3.908882750102787</v>
+        <v>3.946651104670583</v>
       </c>
       <c r="P38">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="Q38">
         <v>50</v>
       </c>
       <c r="R38">
-        <v>0.06071871127633209</v>
+        <v>0.05947955390334572</v>
       </c>
       <c r="S38">
-        <v>0.5102040816326531</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="T38">
-        <v>3.812358276643991</v>
+        <v>3.891782407407408</v>
       </c>
       <c r="U38">
-        <v>0.4279924710979627</v>
+        <v>0.4375520008040036</v>
       </c>
       <c r="V38">
-        <v>0.59186740881929</v>
+        <v>0.6029725721837361</v>
       </c>
       <c r="W38">
-        <v>3.198054853481999</v>
+        <v>3.269485783785472</v>
       </c>
       <c r="X38">
-        <v>4.422564804788584</v>
+        <v>4.505545053261806</v>
       </c>
       <c r="Y38">
-        <v>1.142157022697237E-20</v>
+        <v>3.39842960548138E-21</v>
       </c>
       <c r="Z38">
-        <v>3.42647106809171E-20</v>
+        <v>1.019528881644414E-20</v>
       </c>
     </row>
     <row r="39" spans="1:26">
@@ -7656,49 +7709,49 @@
         <v>126</v>
       </c>
       <c r="F39">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="G39">
         <v>166</v>
       </c>
       <c r="H39">
-        <v>0.9392812887236679</v>
+        <v>0.9405204460966543</v>
       </c>
       <c r="I39">
-        <v>0.1094986807387863</v>
+        <v>0.1093544137022398</v>
       </c>
       <c r="J39">
-        <v>0.8181984755203754</v>
+        <v>0.8171204801639586</v>
       </c>
       <c r="K39">
-        <v>24389469.0727669</v>
+        <v>24404620.06302131</v>
       </c>
       <c r="L39">
         <v>2742223.001044819</v>
       </c>
       <c r="M39">
-        <v>0.9390428368715682</v>
+        <v>0.9396261799868887</v>
       </c>
       <c r="N39">
-        <v>0.1124347148707212</v>
+        <v>0.112364912625701</v>
       </c>
       <c r="O39">
-        <v>0.8111723625833396</v>
+        <v>0.8106687667671205</v>
       </c>
       <c r="P39">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="Q39">
         <v>166</v>
       </c>
       <c r="R39">
-        <v>0.9392812887236679</v>
+        <v>0.9405204460966543</v>
       </c>
       <c r="S39">
-        <v>0.1094986807387863</v>
+        <v>0.1093544137022398</v>
       </c>
       <c r="T39">
-        <v>0.8181984755203754</v>
+        <v>0.8171204801639586</v>
       </c>
     </row>
     <row r="40" spans="1:26">
@@ -7780,67 +7833,67 @@
         <v>125</v>
       </c>
       <c r="F41">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G41">
         <v>28</v>
       </c>
       <c r="H41">
-        <v>0.05514250309789343</v>
+        <v>0.05452292441140025</v>
       </c>
       <c r="I41">
-        <v>0.3146067415730337</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="J41">
-        <v>2.350811485642947</v>
+        <v>2.377525252525253</v>
       </c>
       <c r="K41">
-        <v>1507685.244477059</v>
+        <v>1479512.583717968</v>
       </c>
       <c r="L41">
         <v>436953.8374439232</v>
       </c>
       <c r="M41">
-        <v>0.0580488662897542</v>
+        <v>0.05696416308434589</v>
       </c>
       <c r="N41">
-        <v>0.2898176784873164</v>
+        <v>0.2953363440450586</v>
       </c>
       <c r="O41">
-        <v>2.090920862362545</v>
+        <v>2.130735869532957</v>
       </c>
       <c r="P41">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q41">
         <v>28</v>
       </c>
       <c r="R41">
-        <v>0.05514250309789343</v>
+        <v>0.05452292441140025</v>
       </c>
       <c r="S41">
-        <v>0.3146067415730337</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="T41">
-        <v>2.350811485642947</v>
+        <v>2.377525252525253</v>
       </c>
       <c r="U41">
-        <v>0.2401293107259555</v>
+        <v>0.2429805452147658</v>
       </c>
       <c r="V41">
-        <v>0.4000233042954183</v>
+        <v>0.4042295504262501</v>
       </c>
       <c r="W41">
-        <v>1.79429957181339</v>
+        <v>1.815604629521445</v>
       </c>
       <c r="X41">
-        <v>2.989063023762987</v>
+        <v>3.020493029573925</v>
       </c>
       <c r="Y41">
-        <v>4.127864257371892E-06</v>
+        <v>3.204884358323801E-06</v>
       </c>
       <c r="Z41">
-        <v>6.191796386057837E-06</v>
+        <v>4.807326537485702E-06</v>
       </c>
     </row>
     <row r="42" spans="1:26">
@@ -7860,49 +7913,49 @@
         <v>126</v>
       </c>
       <c r="F42">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="G42">
         <v>188</v>
       </c>
       <c r="H42">
-        <v>0.9448574969021065</v>
+        <v>0.9454770755885997</v>
       </c>
       <c r="I42">
-        <v>0.1232786885245902</v>
+        <v>0.1231979030144168</v>
       </c>
       <c r="J42">
-        <v>0.9211657559198544</v>
+        <v>0.9205621086355031</v>
       </c>
       <c r="K42">
-        <v>24465005.36676352</v>
+        <v>24493178.02752261</v>
       </c>
       <c r="L42">
         <v>3163060.411069466</v>
       </c>
       <c r="M42">
-        <v>0.9419511337102459</v>
+        <v>0.9430358369156542</v>
       </c>
       <c r="N42">
-        <v>0.1292891770776631</v>
+        <v>0.1291404654600225</v>
       </c>
       <c r="O42">
-        <v>0.932770695840081</v>
+        <v>0.9316977998544969</v>
       </c>
       <c r="P42">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="Q42">
         <v>188</v>
       </c>
       <c r="R42">
-        <v>0.9448574969021065</v>
+        <v>0.9454770755885997</v>
       </c>
       <c r="S42">
-        <v>0.1232786885245902</v>
+        <v>0.1231979030144168</v>
       </c>
       <c r="T42">
-        <v>0.9211657559198544</v>
+        <v>0.9205621086355031</v>
       </c>
     </row>
     <row r="43" spans="1:26">
@@ -8392,67 +8445,67 @@
         <v>125</v>
       </c>
       <c r="F50">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G50">
         <v>29</v>
       </c>
       <c r="H50">
-        <v>0.06493506493506493</v>
+        <v>0.06307977736549165</v>
       </c>
       <c r="I50">
-        <v>0.2761904761904762</v>
+        <v>0.2843137254901961</v>
       </c>
       <c r="J50">
-        <v>1.698098859315589</v>
+        <v>1.748042943413107</v>
       </c>
       <c r="K50">
-        <v>1742531.834226764</v>
+        <v>1723728.053831262</v>
       </c>
       <c r="L50">
         <v>498617.4654670961</v>
       </c>
       <c r="M50">
-        <v>0.06747516249418807</v>
+        <v>0.06674703339331883</v>
       </c>
       <c r="N50">
-        <v>0.2861453981346366</v>
+        <v>0.289266897036826</v>
       </c>
       <c r="O50">
-        <v>1.68272469793266</v>
+        <v>1.701081181494951</v>
       </c>
       <c r="P50">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="Q50">
         <v>29</v>
       </c>
       <c r="R50">
-        <v>0.06493506493506493</v>
+        <v>0.06307977736549165</v>
       </c>
       <c r="S50">
-        <v>0.2761904761904762</v>
+        <v>0.2843137254901961</v>
       </c>
       <c r="T50">
-        <v>1.698098859315589</v>
+        <v>1.748042943413107</v>
       </c>
       <c r="U50">
-        <v>0.210726017583872</v>
+        <v>0.217162297621323</v>
       </c>
       <c r="V50">
-        <v>0.3528990429959337</v>
+        <v>0.3626116231425733</v>
       </c>
       <c r="W50">
-        <v>1.29560445031605</v>
+        <v>1.335176559899921</v>
       </c>
       <c r="X50">
-        <v>2.169725294769676</v>
+        <v>2.229441044188369</v>
       </c>
       <c r="Y50">
-        <v>0.001613000911895123</v>
+        <v>0.0009698389365037678</v>
       </c>
       <c r="Z50">
-        <v>0.001613000911895123</v>
+        <v>0.0009698389365037679</v>
       </c>
     </row>
     <row r="51" spans="1:26">
@@ -8472,49 +8525,49 @@
         <v>126</v>
       </c>
       <c r="F51">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="G51">
         <v>234</v>
       </c>
       <c r="H51">
-        <v>0.935064935064935</v>
+        <v>0.9369202226345084</v>
       </c>
       <c r="I51">
-        <v>0.1547619047619048</v>
+        <v>0.1544554455445545</v>
       </c>
       <c r="J51">
-        <v>0.9515209125475286</v>
+        <v>0.9496367127207017</v>
       </c>
       <c r="K51">
-        <v>24082257.16686465</v>
+        <v>24101060.94726015</v>
       </c>
       <c r="L51">
         <v>3892858.180869445</v>
       </c>
       <c r="M51">
-        <v>0.9325248375058119</v>
+        <v>0.9332529666066811</v>
       </c>
       <c r="N51">
-        <v>0.1616483934166155</v>
+        <v>0.1615222744504113</v>
       </c>
       <c r="O51">
-        <v>0.9505997501846544</v>
+        <v>0.9498580870277665</v>
       </c>
       <c r="P51">
-        <v>1512</v>
+        <v>1515</v>
       </c>
       <c r="Q51">
         <v>234</v>
       </c>
       <c r="R51">
-        <v>0.935064935064935</v>
+        <v>0.9369202226345084</v>
       </c>
       <c r="S51">
-        <v>0.1547619047619048</v>
+        <v>0.1544554455445545</v>
       </c>
       <c r="T51">
-        <v>0.9515209125475286</v>
+        <v>0.9496367127207017</v>
       </c>
     </row>
     <row r="52" spans="1:26">
@@ -8596,67 +8649,67 @@
         <v>125</v>
       </c>
       <c r="F53">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G53">
         <v>31</v>
       </c>
       <c r="H53">
-        <v>0.06679035250463822</v>
+        <v>0.06617192331478046</v>
       </c>
       <c r="I53">
-        <v>0.287037037037037</v>
+        <v>0.2897196261682243</v>
       </c>
       <c r="J53">
-        <v>1.764786649767638</v>
+        <v>1.781279982943037</v>
       </c>
       <c r="K53">
-        <v>1715468.213497453</v>
+        <v>1690517.894189597</v>
       </c>
       <c r="L53">
         <v>495205.967595475</v>
       </c>
       <c r="M53">
-        <v>0.06642719185140111</v>
+        <v>0.06546105349082046</v>
       </c>
       <c r="N53">
-        <v>0.2886710250292902</v>
+        <v>0.2929315148319489</v>
       </c>
       <c r="O53">
-        <v>1.697577058938993</v>
+        <v>1.722631564316188</v>
       </c>
       <c r="P53">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q53">
         <v>31</v>
       </c>
       <c r="R53">
-        <v>0.06679035250463822</v>
+        <v>0.06617192331478046</v>
       </c>
       <c r="S53">
-        <v>0.287037037037037</v>
+        <v>0.2897196261682243</v>
       </c>
       <c r="T53">
-        <v>1.764786649767638</v>
+        <v>1.781279982943037</v>
       </c>
       <c r="U53">
-        <v>0.2213299509380661</v>
+        <v>0.2234781858712214</v>
       </c>
       <c r="V53">
-        <v>0.3631533679205407</v>
+        <v>0.3663328794298719</v>
       </c>
       <c r="W53">
-        <v>1.36080049683214</v>
+        <v>1.374008465983897</v>
       </c>
       <c r="X53">
-        <v>2.232771847633134</v>
+        <v>2.252320403186703</v>
       </c>
       <c r="Y53">
-        <v>0.0005342826464999517</v>
+        <v>0.0004457663403827801</v>
       </c>
       <c r="Z53">
-        <v>0.0008014239697499276</v>
+        <v>0.0006686495105741702</v>
       </c>
     </row>
     <row r="54" spans="1:26">
@@ -8676,49 +8729,49 @@
         <v>126</v>
       </c>
       <c r="F54">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="G54">
         <v>232</v>
       </c>
       <c r="H54">
-        <v>0.9332096474953617</v>
+        <v>0.9338280766852195</v>
       </c>
       <c r="I54">
-        <v>0.1537442014579191</v>
+        <v>0.1536423841059603</v>
       </c>
       <c r="J54">
-        <v>0.9452637785454572</v>
+        <v>0.9446377760431093</v>
       </c>
       <c r="K54">
-        <v>24109320.78759396</v>
+        <v>24134271.10690182</v>
       </c>
       <c r="L54">
         <v>3896269.678741066</v>
       </c>
       <c r="M54">
-        <v>0.9335728081485988</v>
+        <v>0.9345389465091795</v>
       </c>
       <c r="N54">
-        <v>0.161608438208097</v>
+        <v>0.1614413653299365</v>
       </c>
       <c r="O54">
-        <v>0.9503647870623276</v>
+        <v>0.9493822877446098</v>
       </c>
       <c r="P54">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="Q54">
         <v>232</v>
       </c>
       <c r="R54">
-        <v>0.9332096474953617</v>
+        <v>0.9338280766852195</v>
       </c>
       <c r="S54">
-        <v>0.1537442014579191</v>
+        <v>0.1536423841059603</v>
       </c>
       <c r="T54">
-        <v>0.9452637785454572</v>
+        <v>0.9446377760431093</v>
       </c>
     </row>
     <row r="55" spans="1:26">
@@ -8896,46 +8949,46 @@
         <v>7</v>
       </c>
       <c r="J2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="K2">
         <v>167</v>
       </c>
       <c r="L2">
-        <v>0.05800756620428751</v>
+        <v>0.05692667987749955</v>
       </c>
       <c r="M2">
-        <v>0.5186335403726708</v>
+        <v>0.5284810126582279</v>
       </c>
       <c r="N2">
-        <v>3.26409839298038</v>
+        <v>3.326074944745831</v>
       </c>
       <c r="O2">
-        <v>2.97607241221415</v>
+        <v>3.035082055020192</v>
       </c>
       <c r="P2">
-        <v>3.550170066569011</v>
+        <v>3.614024477046496</v>
       </c>
       <c r="Q2">
-        <v>1.538604644476722E-54</v>
+        <v>4.362274298554751E-56</v>
       </c>
       <c r="R2">
-        <v>4.615813933430166E-54</v>
+        <v>1.308682289566425E-55</v>
       </c>
       <c r="S2" t="s">
         <v>9</v>
       </c>
       <c r="T2">
-        <v>5276321.036114124</v>
+        <v>5195547.6394781</v>
       </c>
       <c r="U2">
-        <v>0.5159295699622173</v>
+        <v>0.5239505499786756</v>
       </c>
       <c r="V2">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="W2">
-        <v>0.5186335403726708</v>
+        <v>0.5284810126582279</v>
       </c>
       <c r="X2" t="s">
         <v>133</v>
@@ -8970,46 +9023,46 @@
         <v>7</v>
       </c>
       <c r="J3">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="K3">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L3">
-        <v>0.06215096379030805</v>
+        <v>0.06107007746352008</v>
       </c>
       <c r="M3">
-        <v>0.4028985507246377</v>
+        <v>0.4041297935103245</v>
       </c>
       <c r="N3">
-        <v>2.53570278352887</v>
+        <v>2.543451795664185</v>
       </c>
       <c r="O3">
-        <v>2.268117517598033</v>
+        <v>2.273372818285476</v>
       </c>
       <c r="P3">
-        <v>2.812798503446889</v>
+        <v>2.823085511198407</v>
       </c>
       <c r="Q3">
-        <v>1.008072996009283E-29</v>
+        <v>1.897946533132417E-29</v>
       </c>
       <c r="R3">
-        <v>1.512109494013924E-29</v>
+        <v>2.846919799698625E-29</v>
       </c>
       <c r="S3" t="s">
         <v>9</v>
       </c>
       <c r="T3">
-        <v>5599237.991291957</v>
+        <v>5512696.924044427</v>
       </c>
       <c r="U3">
-        <v>0.4161412259808807</v>
+        <v>0.420151697992496</v>
       </c>
       <c r="V3">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="W3">
-        <v>0.4028985507246377</v>
+        <v>0.4041297935103245</v>
       </c>
       <c r="X3" t="s">
         <v>134</v>
@@ -9067,7 +9120,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="B6" t="s">
         <v>136</v>
@@ -9075,7 +9128,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
         <v>137</v>
@@ -9083,7 +9136,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
         <v>136</v>
@@ -9091,7 +9144,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
         <v>137</v>
@@ -9099,7 +9152,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="B10" t="s">
         <v>136</v>
@@ -9107,7 +9160,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
         <v>137</v>

--- a/docs/assets/cases/rules.xlsx
+++ b/docs/assets/cases/rules.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="204">
   <si>
     <t>status</t>
   </si>
@@ -155,7 +155,7 @@
     <t>"AMT_CREDIT"</t>
   </si>
   <si>
-    <t>0.029238900053314865</t>
+    <t>0.031558400005451404</t>
   </si>
   <si>
     <t>{"profile": "production", "direction": "high_risk", "candidate_filter": {"conditions": [{"metric": "lift", "operator": "&gt;=", "value": 1.2}, {"metric": "event_count", "operator": "&gt;=", "value": 3.0}, {"metric": "coverage", "operator": "&gt;=", "value": 0.01}, {"metric": "coverage", "operator": "&lt;=", "value": 0.5}], "targets": "primary", "target_scope": "all", "slice_pass_rate": null}, "validation_filter": {"conditions": [{"metric": "lift", "operator": "&gt;=", "value": 2.0}, {"metric": "event_count", "operator": "&gt;=", "value": 3.0}, {"metric": "coverage", "operator": "&gt;=", "value": 0.01}, {"metric": "coverage", "operator": "&lt;=", "value": 0.5}], "targets": "primary", "target_scope": "all", "slice_pass_rate": 0.8}, "grade_filters": {}, "selection_strategy": "ranked", "top_k": 10, "max_candidates": 100000, "iou_threshold": 0.3, "batch_size": 100, "iou_batch_size": 512, "max_rounds": 10, "random_state": 42, "on_generator_error": "raise", "confidence_level": 0.95, "max_fdr": 0.05, "min_time_slices": 3}</t>
@@ -422,12 +422,15 @@
     <t>display_name</t>
   </si>
   <si>
+    <t>dtype</t>
+  </si>
+  <si>
+    <t>data_source</t>
+  </si>
+  <si>
     <t>description</t>
   </si>
   <si>
-    <t>data_source</t>
-  </si>
-  <si>
     <t>unit</t>
   </si>
   <si>
@@ -437,12 +440,12 @@
     <t>外部来源分 3</t>
   </si>
   <si>
+    <t>Home Credit 2018 application_{train|test}.csv</t>
+  </si>
+  <si>
     <t>Normalized score from external data source</t>
   </si>
   <si>
-    <t>Home Credit 2018 application_{train|test}.csv</t>
-  </si>
-  <si>
     <t>归一化值（无量纲）</t>
   </si>
   <si>
@@ -557,7 +560,7 @@
     <t>"0train only; fixed quantile cutpoints"</t>
   </si>
   <si>
-    <t>{"mr_d07e3095ba389c1a01c8":{"kind":"development_cell","region":{"x_bin":"b0","y_bin":"b0"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":20805,"members_by_dataset":[{"dataset_flag":"0train","total_count":12556,"observed_count":12556},{"dataset_flag":"1val","total_count":1792,"observed_count":1792},{"dataset_flag":"2test","total_count":1829,"observed_count":1829},{"dataset_flag":"3oot","total_count":1757,"observed_count":1757},{"dataset_flag":"4_oot_undue","total_count":2871,"observed_count":0}]},"reference":{"report_id":"c1b6eb2c-9baf-41f7-8937-c9ac486c856c","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b0","y_bin":"b0"}}}},"mr_3ca5e53560ff67e37798":{"kind":"development_cell","region":{"x_bin":"b1","y_bin":"b0"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":19596,"members_by_dataset":[{"dataset_flag":"0train","total_count":11520,"observed_count":11520},{"dataset_flag":"1val","total_count":1648,"observed_count":1648},{"dataset_flag":"2test","total_count":1674,"observed_count":1674},{"dataset_flag":"3oot","total_count":1660,"observed_count":1660},{"dataset_flag":"4_oot_undue","total_count":3094,"observed_count":0}]},"reference":{"report_id":"c1b6eb2c-9baf-41f7-8937-c9ac486c856c","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b1","y_bin":"b0"}}}},"mr_845db7263c6cd864dfa5":{"kind":"development_cell","region":{"x_bin":"b0","y_bin":"b1"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":17399,"members_by_dataset":[{"dataset_flag":"0train","total_count":10494,"observed_count":10494},{"dataset_flag":"1val","total_count":1454,"observed_count":1454},{"dataset_flag":"2test","total_count":1503,"observed_count":1503},{"dataset_flag":"3oot","total_count":1502,"observed_count":1502},{"dataset_flag":"4_oot_undue","total_count":2446,"observed_count":0}]},"reference":{"report_id":"c1b6eb2c-9baf-41f7-8937-c9ac486c856c","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b0","y_bin":"b1"}}}},"mr_51438d35dad4e2c45f37":{"kind":"development_cell","region":{"x_bin":"b3","y_bin":"b3"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":20754,"members_by_dataset":[{"dataset_flag":"0train","total_count":12690,"observed_count":12690},{"dataset_flag":"1val","total_count":1892,"observed_count":1892},{"dataset_flag":"2test","total_count":1858,"observed_count":1858},{"dataset_flag":"3oot","total_count":1836,"observed_count":1836},{"dataset_flag":"4_oot_undue","total_count":2478,"observed_count":0}]},"reference":{"report_id":"c1b6eb2c-9baf-41f7-8937-c9ac486c856c","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b3","y_bin":"b3"}}}}}</t>
+    <t>{"mr_d07e3095ba389c1a01c8":{"kind":"development_cell","region":{"x_bin":"b0","y_bin":"b0"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":20805,"members_by_dataset":[{"dataset_flag":"0train","total_count":12556,"observed_count":12556},{"dataset_flag":"1val","total_count":1792,"observed_count":1792},{"dataset_flag":"2test","total_count":1829,"observed_count":1829},{"dataset_flag":"3oot","total_count":1757,"observed_count":1757},{"dataset_flag":"4_oot_undue","total_count":2871,"observed_count":0}]},"reference":{"report_id":"4178f2f6-3d7c-4583-b1da-9d4c0bce24ec","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b0","y_bin":"b0"}}}},"mr_3ca5e53560ff67e37798":{"kind":"development_cell","region":{"x_bin":"b1","y_bin":"b0"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":19596,"members_by_dataset":[{"dataset_flag":"0train","total_count":11520,"observed_count":11520},{"dataset_flag":"1val","total_count":1648,"observed_count":1648},{"dataset_flag":"2test","total_count":1674,"observed_count":1674},{"dataset_flag":"3oot","total_count":1660,"observed_count":1660},{"dataset_flag":"4_oot_undue","total_count":3094,"observed_count":0}]},"reference":{"report_id":"4178f2f6-3d7c-4583-b1da-9d4c0bce24ec","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b1","y_bin":"b0"}}}},"mr_845db7263c6cd864dfa5":{"kind":"development_cell","region":{"x_bin":"b0","y_bin":"b1"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":17399,"members_by_dataset":[{"dataset_flag":"0train","total_count":10494,"observed_count":10494},{"dataset_flag":"1val","total_count":1454,"observed_count":1454},{"dataset_flag":"2test","total_count":1503,"observed_count":1503},{"dataset_flag":"3oot","total_count":1502,"observed_count":1502},{"dataset_flag":"4_oot_undue","total_count":2446,"observed_count":0}]},"reference":{"report_id":"4178f2f6-3d7c-4583-b1da-9d4c0bce24ec","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b0","y_bin":"b1"}}}},"mr_51438d35dad4e2c45f37":{"kind":"development_cell","region":{"x_bin":"b3","y_bin":"b3"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":20754,"members_by_dataset":[{"dataset_flag":"0train","total_count":12690,"observed_count":12690},{"dataset_flag":"1val","total_count":1892,"observed_count":1892},{"dataset_flag":"2test","total_count":1858,"observed_count":1858},{"dataset_flag":"3oot","total_count":1836,"observed_count":1836},{"dataset_flag":"4_oot_undue","total_count":2478,"observed_count":0}]},"reference":{"report_id":"4178f2f6-3d7c-4583-b1da-9d4c0bce24ec","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b3","y_bin":"b3"}}}}}</t>
   </si>
   <si>
     <t>"1val participates in selection; API dataset='validation' is not final independent test"</t>
@@ -599,7 +602,7 @@
     <t>default_ai_queries</t>
   </si>
   <si>
-    <t>"cccd15c5-8fbd-41aa-a82b-f9656e078448"</t>
+    <t>"408b6056-e5a0-4558-88d4-98cbbc56b0ea"</t>
   </si>
   <si>
     <t>"rule"</t>
@@ -614,7 +617,7 @@
     <t>oat64","unit":"dimensionless","meaning":"规则 Wilson 事件率上界 / 同范围总体事件率；保守 Lift 上界","null":"unavailable; inspect status and report parameters"},"p_value":{"dtype":"Float64","unit":"probability","meaning":"按 direction 的单侧事件富集检验 p 值；方法见 evaluator","null":"unavailable; inspect status and report parameters"},"q_value":{"dtype":"Float64","unit":"probability","meaning":"同数据范围、target、slice、group 候选检验族 BH 校正 q 值","null":"unavailable; inspect status and report parameters"},"qualification":{"dtype":"String","unit":"state","meaning":"计算时 RuleSet 资格；快照恢复不会重建部署资格","null":"unavailable; inspect status and report parameters"},"amount_total":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现样本金金额和；amount_col 未提供则 null；币种见 business_context","null":"unavailable; inspect status and report parameters"},"amount_event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_amount / amount_total；零分母 null","null":"unavailable; inspect status and report parameters"},"customer_count":{"dtype":"Null","unit":"count","meaning":"当前已表现范围去重客户数；customer_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"customer_event_rate":{"dtype":"Null","unit":"ratio","meaning":"event_customer_count / customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"explanation":{"dtype":"String","unit":"text","meaning":"当前行所引用验证范围的中文说明；缺指标显示 N/A","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_relation":{"table":"rule_features","key":"rule_id","feature":"feature","roles":{"rule_id":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次"}},"feature_query":"relation"},"rule_features":{"rows":8,"grain":"distinct rule_id / English feature; includes rejected candidates","schema_version":1,"fields":{"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"feature":{"dtype":"String","unit":"identifier","meaning":"AST 提取的英文输入特征 ID；中文名不替代此身份","null":"unavailable; inspect status and report parameters"}},"feature_roles":{"feature":"feature"},"state":"computed","feature_query":"direct"}}</t>
   </si>
   <si>
-    <t>{"mars_version":"0.0.28","source_project":"deimos-rule","source_commit":"e6714c5e795054e44f0c58ad7097668b4117b4a2","target":"TARGET","aux_targets":[],"features":["EXT_SOURCE_2","EXT_SOURCE_3"],"validation_status":"independent","profile":"production","qualification":"validated","group_col":null,"time_col":null,"time_grain":null,"amount_col":"AMT_CREDIT","customer_col":null,"generation_errors":[],"generator_diagnostics":[],"generators":[],"elapsed_seconds":0.029238900053314865,"resolved_spec":{"profile":"production","direction":"high_risk","candidate_filter":{"conditions":[{"metric":"lift","operator":"&gt;=","value":1.2},{"metric":"event_count","operator":"&gt;=","value":3.0},{"metric":"coverage","operator":"&gt;=","value":0.01},{"metric":"coverage","operator":"&lt;=","value":0.5}],"targets":"primary","target_scope":"all","slice_pass_rate":null},"validation_filter":{"conditions":[{"metric":"lift","operator":"&gt;=","value":2.0},{"metric":"event_count","operator":"&gt;=","value":3.0},{"metric":"coverage","operator":"&gt;=","value":0.01},{"metric":"coverage","operator":"&lt;=","value":0.5}],"targets":"primary","target_scope":"all","slice_pass_rate":0.8},"grade_filters":{},"selection_strategy":"ranked","top_k":10,"max_candidates":100000,"iou_threshold":0.3,"batch_size":100,"iou_batch_size":512,"max_rounds":10,"random_state":42,"on_generator_error":"raise","confidence_level":0.95,"max_fdr":0.05,"min_time_slices":3},"validation_summary":{"profile":"production","qualification":"validated","validation_status":"independent","confidence_level":0.95,"max_fdr":0.05,"min_time_slices":3,"selected_count":1,"temporal_assessed":false,"minimum_time_slice_count":0,"minimum_time_slice_pass_rate":null},"slice_definition":{"kind":"not_computed","column":null,"group_precedes_time":true,"overall_value":"__overall__"},"analysis_states":{"slices":"not_computed","interactions":"not_computed","cumulative":"not_computed","bootstrap":"not_computed"},"advanced_analysis":null}</t>
+    <t>{"mars_version":"0.0.28","source_project":"deimos-rule","source_commit":"e6714c5e795054e44f0c58ad7097668b4117b4a2","target":"TARGET","aux_targets":[],"features":["EXT_SOURCE_2","EXT_SOURCE_3"],"validation_status":"independent","profile":"production","qualification":"validated","group_col":null,"time_col":null,"time_grain":null,"amount_col":"AMT_CREDIT","customer_col":null,"generation_errors":[],"generator_diagnostics":[],"generators":[],"elapsed_seconds":0.031558400005451404,"resolved_spec":{"profile":"production","direction":"high_risk","candidate_filter":{"conditions":[{"metric":"lift","operator":"&gt;=","value":1.2},{"metric":"event_count","operator":"&gt;=","value":3.0},{"metric":"coverage","operator":"&gt;=","value":0.01},{"metric":"coverage","operator":"&lt;=","value":0.5}],"targets":"primary","target_scope":"all","slice_pass_rate":null},"validation_filter":{"conditions":[{"metric":"lift","operator":"&gt;=","value":2.0},{"metric":"event_count","operator":"&gt;=","value":3.0},{"metric":"coverage","operator":"&gt;=","value":0.01},{"metric":"coverage","operator":"&lt;=","value":0.5}],"targets":"primary","target_scope":"all","slice_pass_rate":0.8},"grade_filters":{},"selection_strategy":"ranked","top_k":10,"max_candidates":100000,"iou_threshold":0.3,"batch_size":100,"iou_batch_size":512,"max_rounds":10,"random_state":42,"on_generator_error":"raise","confidence_level":0.95,"max_fdr":0.05,"min_time_slices":3},"validation_summary":{"profile":"production","qualification":"validated","validation_status":"independent","confidence_level":0.95,"max_fdr":0.05,"min_time_slices":3,"selected_count":1,"temporal_assessed":false,"minimum_time_slice_count":0,"minimum_time_slice_pass_rate":null},"slice_definition":{"kind":"not_computed","column":null,"group_precedes_time":true,"overall_value":"__overall__"},"analysis_states":{"slices":"not_computed","interactions":"not_computed","cumulative":"not_computed","bootstrap":"not_computed"},"advanced_analysis":null}</t>
   </si>
   <si>
     <t>{"dataset_id":"home-credit-default-risk-2018","computation":"rule","producer":"mars.rule.MarsRuleReport","mars_version":"0.0.28","origin_project":"deimos-rule"}</t>
@@ -1025,18 +1028,18 @@
         <v>11</v>
       </c>
       <c r="C1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1047,10 +1050,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1061,10 +1064,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1075,10 +1078,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1092,7 +1095,7 @@
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1103,10 +1106,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1120,7 +1123,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1131,10 +1134,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1145,10 +1148,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1159,10 +1162,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1173,7 +1176,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s">
         <v>41</v>
@@ -1187,10 +1190,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1201,10 +1204,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -1215,10 +1218,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1232,7 +1235,7 @@
         <v>52</v>
       </c>
       <c r="B16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1243,10 +1246,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -1257,10 +1260,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1271,10 +1274,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1285,10 +1288,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1299,10 +1302,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1313,10 +1316,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1327,10 +1330,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1357,18 +1360,18 @@
         <v>11</v>
       </c>
       <c r="C1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1379,10 +1382,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1393,10 +1396,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -1407,10 +1410,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1421,10 +1424,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -1435,10 +1438,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1452,7 +1455,7 @@
         <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -1463,7 +1466,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B9" t="s">
         <v>36</v>
@@ -1477,10 +1480,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1491,10 +1494,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1505,10 +1508,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -1519,10 +1522,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -1533,10 +1536,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B14" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -3840,10 +3843,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>128</v>
       </c>
@@ -3859,16 +3862,16 @@
       <c r="E1" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>129</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D2" t="s">
         <v>138</v>
@@ -3876,15 +3879,15 @@
       <c r="E2" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>130</v>
       </c>
       <c r="B3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C3" t="s">
         <v>137</v>
       </c>
       <c r="D3" t="s">
@@ -3892,6 +3895,9 @@
       </c>
       <c r="E3" t="s">
         <v>139</v>
+      </c>
+      <c r="F3" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/docs/assets/cases/rules.xlsx
+++ b/docs/assets/cases/rules.xlsx
@@ -155,7 +155,7 @@
     <t>"AMT_CREDIT"</t>
   </si>
   <si>
-    <t>0.031558400005451404</t>
+    <t>0.016896900022402406</t>
   </si>
   <si>
     <t>{"profile": "production", "direction": "high_risk", "candidate_filter": {"conditions": [{"metric": "lift", "operator": "&gt;=", "value": 1.2}, {"metric": "event_count", "operator": "&gt;=", "value": 3.0}, {"metric": "coverage", "operator": "&gt;=", "value": 0.01}, {"metric": "coverage", "operator": "&lt;=", "value": 0.5}], "targets": "primary", "target_scope": "all", "slice_pass_rate": null}, "validation_filter": {"conditions": [{"metric": "lift", "operator": "&gt;=", "value": 2.0}, {"metric": "event_count", "operator": "&gt;=", "value": 3.0}, {"metric": "coverage", "operator": "&gt;=", "value": 0.01}, {"metric": "coverage", "operator": "&lt;=", "value": 0.5}], "targets": "primary", "target_scope": "all", "slice_pass_rate": 0.8}, "grade_filters": {}, "selection_strategy": "ranked", "top_k": 10, "max_candidates": 100000, "iou_threshold": 0.3, "batch_size": 100, "iou_batch_size": 512, "max_rounds": 10, "random_state": 42, "on_generator_error": "raise", "confidence_level": 0.95, "max_fdr": 0.05, "min_time_slices": 3}</t>
@@ -560,7 +560,7 @@
     <t>"0train only; fixed quantile cutpoints"</t>
   </si>
   <si>
-    <t>{"mr_d07e3095ba389c1a01c8":{"kind":"development_cell","region":{"x_bin":"b0","y_bin":"b0"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":20805,"members_by_dataset":[{"dataset_flag":"0train","total_count":12556,"observed_count":12556},{"dataset_flag":"1val","total_count":1792,"observed_count":1792},{"dataset_flag":"2test","total_count":1829,"observed_count":1829},{"dataset_flag":"3oot","total_count":1757,"observed_count":1757},{"dataset_flag":"4_oot_undue","total_count":2871,"observed_count":0}]},"reference":{"report_id":"4178f2f6-3d7c-4583-b1da-9d4c0bce24ec","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b0","y_bin":"b0"}}}},"mr_3ca5e53560ff67e37798":{"kind":"development_cell","region":{"x_bin":"b1","y_bin":"b0"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":19596,"members_by_dataset":[{"dataset_flag":"0train","total_count":11520,"observed_count":11520},{"dataset_flag":"1val","total_count":1648,"observed_count":1648},{"dataset_flag":"2test","total_count":1674,"observed_count":1674},{"dataset_flag":"3oot","total_count":1660,"observed_count":1660},{"dataset_flag":"4_oot_undue","total_count":3094,"observed_count":0}]},"reference":{"report_id":"4178f2f6-3d7c-4583-b1da-9d4c0bce24ec","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b1","y_bin":"b0"}}}},"mr_845db7263c6cd864dfa5":{"kind":"development_cell","region":{"x_bin":"b0","y_bin":"b1"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":17399,"members_by_dataset":[{"dataset_flag":"0train","total_count":10494,"observed_count":10494},{"dataset_flag":"1val","total_count":1454,"observed_count":1454},{"dataset_flag":"2test","total_count":1503,"observed_count":1503},{"dataset_flag":"3oot","total_count":1502,"observed_count":1502},{"dataset_flag":"4_oot_undue","total_count":2446,"observed_count":0}]},"reference":{"report_id":"4178f2f6-3d7c-4583-b1da-9d4c0bce24ec","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b0","y_bin":"b1"}}}},"mr_51438d35dad4e2c45f37":{"kind":"development_cell","region":{"x_bin":"b3","y_bin":"b3"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":20754,"members_by_dataset":[{"dataset_flag":"0train","total_count":12690,"observed_count":12690},{"dataset_flag":"1val","total_count":1892,"observed_count":1892},{"dataset_flag":"2test","total_count":1858,"observed_count":1858},{"dataset_flag":"3oot","total_count":1836,"observed_count":1836},{"dataset_flag":"4_oot_undue","total_count":2478,"observed_count":0}]},"reference":{"report_id":"4178f2f6-3d7c-4583-b1da-9d4c0bce24ec","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b3","y_bin":"b3"}}}}}</t>
+    <t>{"mr_d07e3095ba389c1a01c8":{"kind":"development_cell","region":{"x_bin":"b0","y_bin":"b0"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":20805,"members_by_dataset":[{"dataset_flag":"0train","total_count":12556,"observed_count":12556},{"dataset_flag":"1val","total_count":1792,"observed_count":1792},{"dataset_flag":"2test","total_count":1829,"observed_count":1829},{"dataset_flag":"3oot","total_count":1757,"observed_count":1757},{"dataset_flag":"4_oot_undue","total_count":2871,"observed_count":0}]},"reference":{"report_id":"5ba145f2-6fd0-44ab-85fa-de9dee9a690c","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b0","y_bin":"b0"}}}},"mr_3ca5e53560ff67e37798":{"kind":"development_cell","region":{"x_bin":"b1","y_bin":"b0"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":19596,"members_by_dataset":[{"dataset_flag":"0train","total_count":11520,"observed_count":11520},{"dataset_flag":"1val","total_count":1648,"observed_count":1648},{"dataset_flag":"2test","total_count":1674,"observed_count":1674},{"dataset_flag":"3oot","total_count":1660,"observed_count":1660},{"dataset_flag":"4_oot_undue","total_count":3094,"observed_count":0}]},"reference":{"report_id":"5ba145f2-6fd0-44ab-85fa-de9dee9a690c","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b1","y_bin":"b0"}}}},"mr_845db7263c6cd864dfa5":{"kind":"development_cell","region":{"x_bin":"b0","y_bin":"b1"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":17399,"members_by_dataset":[{"dataset_flag":"0train","total_count":10494,"observed_count":10494},{"dataset_flag":"1val","total_count":1454,"observed_count":1454},{"dataset_flag":"2test","total_count":1503,"observed_count":1503},{"dataset_flag":"3oot","total_count":1502,"observed_count":1502},{"dataset_flag":"4_oot_undue","total_count":2446,"observed_count":0}]},"reference":{"report_id":"5ba145f2-6fd0-44ab-85fa-de9dee9a690c","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b0","y_bin":"b1"}}}},"mr_51438d35dad4e2c45f37":{"kind":"development_cell","region":{"x_bin":"b3","y_bin":"b3"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":20754,"members_by_dataset":[{"dataset_flag":"0train","total_count":12690,"observed_count":12690},{"dataset_flag":"1val","total_count":1892,"observed_count":1892},{"dataset_flag":"2test","total_count":1858,"observed_count":1858},{"dataset_flag":"3oot","total_count":1836,"observed_count":1836},{"dataset_flag":"4_oot_undue","total_count":2478,"observed_count":0}]},"reference":{"report_id":"5ba145f2-6fd0-44ab-85fa-de9dee9a690c","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b3","y_bin":"b3"}}}}}</t>
   </si>
   <si>
     <t>"1val participates in selection; API dataset='validation' is not final independent test"</t>
@@ -602,7 +602,7 @@
     <t>default_ai_queries</t>
   </si>
   <si>
-    <t>"408b6056-e5a0-4558-88d4-98cbbc56b0ea"</t>
+    <t>"57f3678d-f9b3-4d5c-86f8-9c36843f32d3"</t>
   </si>
   <si>
     <t>"rule"</t>
@@ -617,7 +617,7 @@
     <t>oat64","unit":"dimensionless","meaning":"规则 Wilson 事件率上界 / 同范围总体事件率；保守 Lift 上界","null":"unavailable; inspect status and report parameters"},"p_value":{"dtype":"Float64","unit":"probability","meaning":"按 direction 的单侧事件富集检验 p 值；方法见 evaluator","null":"unavailable; inspect status and report parameters"},"q_value":{"dtype":"Float64","unit":"probability","meaning":"同数据范围、target、slice、group 候选检验族 BH 校正 q 值","null":"unavailable; inspect status and report parameters"},"qualification":{"dtype":"String","unit":"state","meaning":"计算时 RuleSet 资格；快照恢复不会重建部署资格","null":"unavailable; inspect status and report parameters"},"amount_total":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现样本金金额和；amount_col 未提供则 null；币种见 business_context","null":"unavailable; inspect status and report parameters"},"amount_event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_amount / amount_total；零分母 null","null":"unavailable; inspect status and report parameters"},"customer_count":{"dtype":"Null","unit":"count","meaning":"当前已表现范围去重客户数；customer_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"customer_event_rate":{"dtype":"Null","unit":"ratio","meaning":"event_customer_count / customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"explanation":{"dtype":"String","unit":"text","meaning":"当前行所引用验证范围的中文说明；缺指标显示 N/A","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_relation":{"table":"rule_features","key":"rule_id","feature":"feature","roles":{"rule_id":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次"}},"feature_query":"relation"},"rule_features":{"rows":8,"grain":"distinct rule_id / English feature; includes rejected candidates","schema_version":1,"fields":{"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"feature":{"dtype":"String","unit":"identifier","meaning":"AST 提取的英文输入特征 ID；中文名不替代此身份","null":"unavailable; inspect status and report parameters"}},"feature_roles":{"feature":"feature"},"state":"computed","feature_query":"direct"}}</t>
   </si>
   <si>
-    <t>{"mars_version":"0.0.28","source_project":"deimos-rule","source_commit":"e6714c5e795054e44f0c58ad7097668b4117b4a2","target":"TARGET","aux_targets":[],"features":["EXT_SOURCE_2","EXT_SOURCE_3"],"validation_status":"independent","profile":"production","qualification":"validated","group_col":null,"time_col":null,"time_grain":null,"amount_col":"AMT_CREDIT","customer_col":null,"generation_errors":[],"generator_diagnostics":[],"generators":[],"elapsed_seconds":0.031558400005451404,"resolved_spec":{"profile":"production","direction":"high_risk","candidate_filter":{"conditions":[{"metric":"lift","operator":"&gt;=","value":1.2},{"metric":"event_count","operator":"&gt;=","value":3.0},{"metric":"coverage","operator":"&gt;=","value":0.01},{"metric":"coverage","operator":"&lt;=","value":0.5}],"targets":"primary","target_scope":"all","slice_pass_rate":null},"validation_filter":{"conditions":[{"metric":"lift","operator":"&gt;=","value":2.0},{"metric":"event_count","operator":"&gt;=","value":3.0},{"metric":"coverage","operator":"&gt;=","value":0.01},{"metric":"coverage","operator":"&lt;=","value":0.5}],"targets":"primary","target_scope":"all","slice_pass_rate":0.8},"grade_filters":{},"selection_strategy":"ranked","top_k":10,"max_candidates":100000,"iou_threshold":0.3,"batch_size":100,"iou_batch_size":512,"max_rounds":10,"random_state":42,"on_generator_error":"raise","confidence_level":0.95,"max_fdr":0.05,"min_time_slices":3},"validation_summary":{"profile":"production","qualification":"validated","validation_status":"independent","confidence_level":0.95,"max_fdr":0.05,"min_time_slices":3,"selected_count":1,"temporal_assessed":false,"minimum_time_slice_count":0,"minimum_time_slice_pass_rate":null},"slice_definition":{"kind":"not_computed","column":null,"group_precedes_time":true,"overall_value":"__overall__"},"analysis_states":{"slices":"not_computed","interactions":"not_computed","cumulative":"not_computed","bootstrap":"not_computed"},"advanced_analysis":null}</t>
+    <t>{"mars_version":"0.0.28","source_project":"deimos-rule","source_commit":"e6714c5e795054e44f0c58ad7097668b4117b4a2","target":"TARGET","aux_targets":[],"features":["EXT_SOURCE_2","EXT_SOURCE_3"],"validation_status":"independent","profile":"production","qualification":"validated","group_col":null,"time_col":null,"time_grain":null,"amount_col":"AMT_CREDIT","customer_col":null,"generation_errors":[],"generator_diagnostics":[],"generators":[],"elapsed_seconds":0.016896900022402406,"resolved_spec":{"profile":"production","direction":"high_risk","candidate_filter":{"conditions":[{"metric":"lift","operator":"&gt;=","value":1.2},{"metric":"event_count","operator":"&gt;=","value":3.0},{"metric":"coverage","operator":"&gt;=","value":0.01},{"metric":"coverage","operator":"&lt;=","value":0.5}],"targets":"primary","target_scope":"all","slice_pass_rate":null},"validation_filter":{"conditions":[{"metric":"lift","operator":"&gt;=","value":2.0},{"metric":"event_count","operator":"&gt;=","value":3.0},{"metric":"coverage","operator":"&gt;=","value":0.01},{"metric":"coverage","operator":"&lt;=","value":0.5}],"targets":"primary","target_scope":"all","slice_pass_rate":0.8},"grade_filters":{},"selection_strategy":"ranked","top_k":10,"max_candidates":100000,"iou_threshold":0.3,"batch_size":100,"iou_batch_size":512,"max_rounds":10,"random_state":42,"on_generator_error":"raise","confidence_level":0.95,"max_fdr":0.05,"min_time_slices":3},"validation_summary":{"profile":"production","qualification":"validated","validation_status":"independent","confidence_level":0.95,"max_fdr":0.05,"min_time_slices":3,"selected_count":1,"temporal_assessed":false,"minimum_time_slice_count":0,"minimum_time_slice_pass_rate":null},"slice_definition":{"kind":"not_computed","column":null,"group_precedes_time":true,"overall_value":"__overall__"},"analysis_states":{"slices":"not_computed","interactions":"not_computed","cumulative":"not_computed","bootstrap":"not_computed"},"advanced_analysis":null}</t>
   </si>
   <si>
     <t>{"dataset_id":"home-credit-default-risk-2018","computation":"rule","producer":"mars.rule.MarsRuleReport","mars_version":"0.0.28","origin_project":"deimos-rule"}</t>

--- a/docs/assets/cases/rules.xlsx
+++ b/docs/assets/cases/rules.xlsx
@@ -155,7 +155,7 @@
     <t>"AMT_CREDIT"</t>
   </si>
   <si>
-    <t>0.016896900022402406</t>
+    <t>0.01313450001180172</t>
   </si>
   <si>
     <t>{"profile": "production", "direction": "high_risk", "candidate_filter": {"conditions": [{"metric": "lift", "operator": "&gt;=", "value": 1.2}, {"metric": "event_count", "operator": "&gt;=", "value": 3.0}, {"metric": "coverage", "operator": "&gt;=", "value": 0.01}, {"metric": "coverage", "operator": "&lt;=", "value": 0.5}], "targets": "primary", "target_scope": "all", "slice_pass_rate": null}, "validation_filter": {"conditions": [{"metric": "lift", "operator": "&gt;=", "value": 2.0}, {"metric": "event_count", "operator": "&gt;=", "value": 3.0}, {"metric": "coverage", "operator": "&gt;=", "value": 0.01}, {"metric": "coverage", "operator": "&lt;=", "value": 0.5}], "targets": "primary", "target_scope": "all", "slice_pass_rate": 0.8}, "grade_filters": {}, "selection_strategy": "ranked", "top_k": 10, "max_candidates": 100000, "iou_threshold": 0.3, "batch_size": 100, "iou_batch_size": 512, "max_rounds": 10, "random_state": 42, "on_generator_error": "raise", "confidence_level": 0.95, "max_fdr": 0.05, "min_time_slices": 3}</t>
@@ -560,7 +560,7 @@
     <t>"0train only; fixed quantile cutpoints"</t>
   </si>
   <si>
-    <t>{"mr_d07e3095ba389c1a01c8":{"kind":"development_cell","region":{"x_bin":"b0","y_bin":"b0"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":20805,"members_by_dataset":[{"dataset_flag":"0train","total_count":12556,"observed_count":12556},{"dataset_flag":"1val","total_count":1792,"observed_count":1792},{"dataset_flag":"2test","total_count":1829,"observed_count":1829},{"dataset_flag":"3oot","total_count":1757,"observed_count":1757},{"dataset_flag":"4_oot_undue","total_count":2871,"observed_count":0}]},"reference":{"report_id":"5ba145f2-6fd0-44ab-85fa-de9dee9a690c","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b0","y_bin":"b0"}}}},"mr_3ca5e53560ff67e37798":{"kind":"development_cell","region":{"x_bin":"b1","y_bin":"b0"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":19596,"members_by_dataset":[{"dataset_flag":"0train","total_count":11520,"observed_count":11520},{"dataset_flag":"1val","total_count":1648,"observed_count":1648},{"dataset_flag":"2test","total_count":1674,"observed_count":1674},{"dataset_flag":"3oot","total_count":1660,"observed_count":1660},{"dataset_flag":"4_oot_undue","total_count":3094,"observed_count":0}]},"reference":{"report_id":"5ba145f2-6fd0-44ab-85fa-de9dee9a690c","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b1","y_bin":"b0"}}}},"mr_845db7263c6cd864dfa5":{"kind":"development_cell","region":{"x_bin":"b0","y_bin":"b1"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":17399,"members_by_dataset":[{"dataset_flag":"0train","total_count":10494,"observed_count":10494},{"dataset_flag":"1val","total_count":1454,"observed_count":1454},{"dataset_flag":"2test","total_count":1503,"observed_count":1503},{"dataset_flag":"3oot","total_count":1502,"observed_count":1502},{"dataset_flag":"4_oot_undue","total_count":2446,"observed_count":0}]},"reference":{"report_id":"5ba145f2-6fd0-44ab-85fa-de9dee9a690c","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b0","y_bin":"b1"}}}},"mr_51438d35dad4e2c45f37":{"kind":"development_cell","region":{"x_bin":"b3","y_bin":"b3"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":20754,"members_by_dataset":[{"dataset_flag":"0train","total_count":12690,"observed_count":12690},{"dataset_flag":"1val","total_count":1892,"observed_count":1892},{"dataset_flag":"2test","total_count":1858,"observed_count":1858},{"dataset_flag":"3oot","total_count":1836,"observed_count":1836},{"dataset_flag":"4_oot_undue","total_count":2478,"observed_count":0}]},"reference":{"report_id":"5ba145f2-6fd0-44ab-85fa-de9dee9a690c","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b3","y_bin":"b3"}}}}}</t>
+    <t>{"mr_d07e3095ba389c1a01c8":{"kind":"development_cell","region":{"x_bin":"b0","y_bin":"b0"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":20805,"members_by_dataset":[{"dataset_flag":"0train","total_count":12556,"observed_count":12556},{"dataset_flag":"1val","total_count":1792,"observed_count":1792},{"dataset_flag":"2test","total_count":1829,"observed_count":1829},{"dataset_flag":"3oot","total_count":1757,"observed_count":1757},{"dataset_flag":"4_oot_undue","total_count":2871,"observed_count":0}]},"reference":{"report_id":"77208fb5-bb0e-424b-9ddb-3b5b24790fbd","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b0","y_bin":"b0"}}}},"mr_3ca5e53560ff67e37798":{"kind":"development_cell","region":{"x_bin":"b1","y_bin":"b0"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":19596,"members_by_dataset":[{"dataset_flag":"0train","total_count":11520,"observed_count":11520},{"dataset_flag":"1val","total_count":1648,"observed_count":1648},{"dataset_flag":"2test","total_count":1674,"observed_count":1674},{"dataset_flag":"3oot","total_count":1660,"observed_count":1660},{"dataset_flag":"4_oot_undue","total_count":3094,"observed_count":0}]},"reference":{"report_id":"77208fb5-bb0e-424b-9ddb-3b5b24790fbd","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b1","y_bin":"b0"}}}},"mr_845db7263c6cd864dfa5":{"kind":"development_cell","region":{"x_bin":"b0","y_bin":"b1"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":17399,"members_by_dataset":[{"dataset_flag":"0train","total_count":10494,"observed_count":10494},{"dataset_flag":"1val","total_count":1454,"observed_count":1454},{"dataset_flag":"2test","total_count":1503,"observed_count":1503},{"dataset_flag":"3oot","total_count":1502,"observed_count":1502},{"dataset_flag":"4_oot_undue","total_count":2446,"observed_count":0}]},"reference":{"report_id":"77208fb5-bb0e-424b-9ddb-3b5b24790fbd","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b0","y_bin":"b1"}}}},"mr_51438d35dad4e2c45f37":{"kind":"development_cell","region":{"x_bin":"b3","y_bin":"b3"},"member_check":{"verified":true,"scope":"all supplied rows; exact SK_ID_CURR membership; IDs not saved","member_count":20754,"members_by_dataset":[{"dataset_flag":"0train","total_count":12690,"observed_count":12690},{"dataset_flag":"1val","total_count":1892,"observed_count":1892},{"dataset_flag":"2test","total_count":1858,"observed_count":1858},{"dataset_flag":"3oot","total_count":1836,"observed_count":1836},{"dataset_flag":"4_oot_undue","total_count":2478,"observed_count":0}]},"reference":{"report_id":"77208fb5-bb0e-424b-9ddb-3b5b24790fbd","table":"cells","query":{"offset":0,"limit":1,"filters":{"group":"0train","target":"TARGET","period":"Total","x_bin":"b3","y_bin":"b3"}}}}}</t>
   </si>
   <si>
     <t>"1val participates in selection; API dataset='validation' is not final independent test"</t>
@@ -602,7 +602,7 @@
     <t>default_ai_queries</t>
   </si>
   <si>
-    <t>"57f3678d-f9b3-4d5c-86f8-9c36843f32d3"</t>
+    <t>"dc3aa22f-37ad-4b2e-8872-9fbda42bcb4b"</t>
   </si>
   <si>
     <t>"rule"</t>
@@ -617,7 +617,7 @@
     <t>oat64","unit":"dimensionless","meaning":"规则 Wilson 事件率上界 / 同范围总体事件率；保守 Lift 上界","null":"unavailable; inspect status and report parameters"},"p_value":{"dtype":"Float64","unit":"probability","meaning":"按 direction 的单侧事件富集检验 p 值；方法见 evaluator","null":"unavailable; inspect status and report parameters"},"q_value":{"dtype":"Float64","unit":"probability","meaning":"同数据范围、target、slice、group 候选检验族 BH 校正 q 值","null":"unavailable; inspect status and report parameters"},"qualification":{"dtype":"String","unit":"state","meaning":"计算时 RuleSet 资格；快照恢复不会重建部署资格","null":"unavailable; inspect status and report parameters"},"amount_total":{"dtype":"Float64","unit":"unknown_business_unit","meaning":"当前范围已表现样本金金额和；amount_col 未提供则 null；币种见 business_context","null":"unavailable; inspect status and report parameters"},"amount_event_rate":{"dtype":"Float64","unit":"ratio","meaning":"event_amount / amount_total；零分母 null","null":"unavailable; inspect status and report parameters"},"customer_count":{"dtype":"Null","unit":"count","meaning":"当前已表现范围去重客户数；customer_col 未提供则 null","null":"unavailable; inspect status and report parameters"},"customer_event_rate":{"dtype":"Null","unit":"ratio","meaning":"event_customer_count / customer_count；不可跨规则相加","null":"unavailable; inspect status and report parameters"},"explanation":{"dtype":"String","unit":"text","meaning":"当前行所引用验证范围的中文说明；缺指标显示 N/A","null":"unavailable; inspect status and report parameters"}},"state":"computed","feature_relation":{"table":"rule_features","key":"rule_id","feature":"feature","roles":{"rule_id":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次"}},"feature_query":"relation"},"rule_features":{"rows":8,"grain":"distinct rule_id / English feature; includes rejected candidates","schema_version":1,"fields":{"rule_id":{"dtype":"String","unit":"identifier","meaning":"规范 DSL 的稳定哈希 ID；同 ID 可出现在不同 dataset、target 或轮次","null":"unavailable; inspect status and report parameters"},"feature":{"dtype":"String","unit":"identifier","meaning":"AST 提取的英文输入特征 ID；中文名不替代此身份","null":"unavailable; inspect status and report parameters"}},"feature_roles":{"feature":"feature"},"state":"computed","feature_query":"direct"}}</t>
   </si>
   <si>
-    <t>{"mars_version":"0.0.28","source_project":"deimos-rule","source_commit":"e6714c5e795054e44f0c58ad7097668b4117b4a2","target":"TARGET","aux_targets":[],"features":["EXT_SOURCE_2","EXT_SOURCE_3"],"validation_status":"independent","profile":"production","qualification":"validated","group_col":null,"time_col":null,"time_grain":null,"amount_col":"AMT_CREDIT","customer_col":null,"generation_errors":[],"generator_diagnostics":[],"generators":[],"elapsed_seconds":0.016896900022402406,"resolved_spec":{"profile":"production","direction":"high_risk","candidate_filter":{"conditions":[{"metric":"lift","operator":"&gt;=","value":1.2},{"metric":"event_count","operator":"&gt;=","value":3.0},{"metric":"coverage","operator":"&gt;=","value":0.01},{"metric":"coverage","operator":"&lt;=","value":0.5}],"targets":"primary","target_scope":"all","slice_pass_rate":null},"validation_filter":{"conditions":[{"metric":"lift","operator":"&gt;=","value":2.0},{"metric":"event_count","operator":"&gt;=","value":3.0},{"metric":"coverage","operator":"&gt;=","value":0.01},{"metric":"coverage","operator":"&lt;=","value":0.5}],"targets":"primary","target_scope":"all","slice_pass_rate":0.8},"grade_filters":{},"selection_strategy":"ranked","top_k":10,"max_candidates":100000,"iou_threshold":0.3,"batch_size":100,"iou_batch_size":512,"max_rounds":10,"random_state":42,"on_generator_error":"raise","confidence_level":0.95,"max_fdr":0.05,"min_time_slices":3},"validation_summary":{"profile":"production","qualification":"validated","validation_status":"independent","confidence_level":0.95,"max_fdr":0.05,"min_time_slices":3,"selected_count":1,"temporal_assessed":false,"minimum_time_slice_count":0,"minimum_time_slice_pass_rate":null},"slice_definition":{"kind":"not_computed","column":null,"group_precedes_time":true,"overall_value":"__overall__"},"analysis_states":{"slices":"not_computed","interactions":"not_computed","cumulative":"not_computed","bootstrap":"not_computed"},"advanced_analysis":null}</t>
+    <t>{"mars_version":"0.0.28","source_project":"deimos-rule","source_commit":"e6714c5e795054e44f0c58ad7097668b4117b4a2","target":"TARGET","aux_targets":[],"features":["EXT_SOURCE_2","EXT_SOURCE_3"],"validation_status":"independent","profile":"production","qualification":"validated","group_col":null,"time_col":null,"time_grain":null,"amount_col":"AMT_CREDIT","customer_col":null,"generation_errors":[],"generator_diagnostics":[],"generators":[],"elapsed_seconds":0.01313450001180172,"resolved_spec":{"profile":"production","direction":"high_risk","candidate_filter":{"conditions":[{"metric":"lift","operator":"&gt;=","value":1.2},{"metric":"event_count","operator":"&gt;=","value":3.0},{"metric":"coverage","operator":"&gt;=","value":0.01},{"metric":"coverage","operator":"&lt;=","value":0.5}],"targets":"primary","target_scope":"all","slice_pass_rate":null},"validation_filter":{"conditions":[{"metric":"lift","operator":"&gt;=","value":2.0},{"metric":"event_count","operator":"&gt;=","value":3.0},{"metric":"coverage","operator":"&gt;=","value":0.01},{"metric":"coverage","operator":"&lt;=","value":0.5}],"targets":"primary","target_scope":"all","slice_pass_rate":0.8},"grade_filters":{},"selection_strategy":"ranked","top_k":10,"max_candidates":100000,"iou_threshold":0.3,"batch_size":100,"iou_batch_size":512,"max_rounds":10,"random_state":42,"on_generator_error":"raise","confidence_level":0.95,"max_fdr":0.05,"min_time_slices":3},"validation_summary":{"profile":"production","qualification":"validated","validation_status":"independent","confidence_level":0.95,"max_fdr":0.05,"min_time_slices":3,"selected_count":1,"temporal_assessed":false,"minimum_time_slice_count":0,"minimum_time_slice_pass_rate":null},"slice_definition":{"kind":"not_computed","column":null,"group_precedes_time":true,"overall_value":"__overall__"},"analysis_states":{"slices":"not_computed","interactions":"not_computed","cumulative":"not_computed","bootstrap":"not_computed"},"advanced_analysis":null}</t>
   </si>
   <si>
     <t>{"dataset_id":"home-credit-default-risk-2018","computation":"rule","producer":"mars.rule.MarsRuleReport","mars_version":"0.0.28","origin_project":"deimos-rule"}</t>
